--- a/20_設計書/インフラ/パラメータシート.xlsx
+++ b/20_設計書/インフラ/パラメータシート.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\project\hrs_環境証明書\20_設計書\インフラ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E290EC-FDA2-4AF4-825F-68F26CA536B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AF0FED0-A4A0-400A-98F8-CE1D3AE7FCAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5685" yWindow="450" windowWidth="21780" windowHeight="12555" tabRatio="859" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4860" yWindow="795" windowWidth="22950" windowHeight="14055" tabRatio="859" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="2" r:id="rId1"/>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="82">
   <si>
     <t>HRS殿</t>
     <rPh sb="3" eb="4">
@@ -542,6 +542,50 @@
     <t>https://stg-chemical-substance.hirose.com/login/?uid={token}</t>
     <phoneticPr fontId="52"/>
   </si>
+  <si>
+    <t>ログインAPI</t>
+    <phoneticPr fontId="52"/>
+  </si>
+  <si>
+    <t>https://stg-storefront.hrs-product.com/api/v1/external/session/user</t>
+    <phoneticPr fontId="52"/>
+  </si>
+  <si>
+    <t>https://www.hirose.com/api/v1/external/session/user</t>
+    <phoneticPr fontId="52"/>
+  </si>
+  <si>
+    <t>WEB画面</t>
+    <rPh sb="3" eb="5">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="52"/>
+  </si>
+  <si>
+    <t>https://hirose.com/ja/product/</t>
+    <phoneticPr fontId="52"/>
+  </si>
+  <si>
+    <t>https://stg-storefront.hrs-product.com/ja/product/</t>
+    <phoneticPr fontId="52"/>
+  </si>
+  <si>
+    <t>mig+a-aa_aa.co.jp@distor-a.site</t>
+    <phoneticPr fontId="52"/>
+  </si>
+  <si>
+    <t>Hrs12345</t>
+    <phoneticPr fontId="52"/>
+  </si>
+  <si>
+    <t>arn:aws:iam::064032700625:role/Chem-prd-EcsWebService-TaskRole</t>
+  </si>
+  <si>
+    <t>arn:aws:iam::064032700625:role/Chem-prd-CertificatePollingTask-TaskRole</t>
+  </si>
+  <si>
+    <t>arn:aws:iam::064032700625:role/Chem-prd-ProductMasterSyncTask-TaskRole</t>
+  </si>
 </sst>
 </file>
 
@@ -552,7 +596,7 @@
     <numFmt numFmtId="177" formatCode="0.00_)"/>
     <numFmt numFmtId="178" formatCode="#,##0.00;[Red]\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="59">
+  <fonts count="58">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -940,15 +984,6 @@
       <family val="2"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -1296,7 +1331,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="187">
+  <cellStyleXfs count="186">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1823,11 +1858,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1888,13 +1920,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="3" xfId="186" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1918,7 +1947,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1927,6 +1956,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="14" fontId="55" fillId="12" borderId="0" xfId="48" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2086,17 +2139,8 @@
     <xf numFmtId="0" fontId="13" fillId="14" borderId="13" xfId="49" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="187">
+  <cellStyles count="186">
     <cellStyle name="0301" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="0_x0014_標準_F_02?P_Dd080301" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Calc Currency (0)" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
@@ -2140,7 +2184,6 @@
     <cellStyle name="subhead" xfId="41" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
     <cellStyle name="title" xfId="42" xr:uid="{00000000-0005-0000-0000-000029000000}"/>
     <cellStyle name="UploadThisRowValue" xfId="43" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
-    <cellStyle name="ハイパーリンク" xfId="186" builtinId="8"/>
     <cellStyle name="_x001d__x000c_K_x0014__x000d_&gt;V_x0001_&gt;_x0014_n_x001e__x0007__x0001__x0001_" xfId="44" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
     <cellStyle name="標準 10" xfId="183" xr:uid="{EA538841-B3F7-4189-AE1D-AD4B02F64DDE}"/>
@@ -3294,29 +3337,8 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>      "arn:aws:iam::064032700625:role/Chem-prd-Certificat</a:t>
+            <a:t>      "arn:aws:iam::064032700625:role/Chem-prd-CertificatePollingTask-TaskRole"</a:t>
           </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ja-JP" sz="1100" b="0" i="1">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>e</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" altLang="ja-JP" sz="1100" b="0">
-            <a:solidFill>
-              <a:schemeClr val="dk1"/>
-            </a:solidFill>
-            <a:effectLst/>
-            <a:latin typeface="+mn-lt"/>
-            <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="+mn-cs"/>
-          </a:endParaRPr>
         </a:p>
         <a:p>
           <a:r>
@@ -3985,16 +4007,16 @@
     <row r="20" spans="2:8" ht="14.25" customHeight="1"/>
     <row r="21" spans="2:8" ht="14.25" customHeight="1"/>
     <row r="22" spans="2:8" ht="14.25" customHeight="1">
-      <c r="B22" s="35" t="str">
+      <c r="B22" s="42" t="str">
         <f ca="1">TEXT(変更来歴!AT2,"yyyy年 mm月 dd日") &amp; " " &amp; 変更来歴!AT3</f>
         <v>1900年 01月 00日 1.0</v>
       </c>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="36"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
     </row>
     <row r="23" spans="2:8" ht="14.25" customHeight="1"/>
     <row r="24" spans="2:8" ht="14.25" customHeight="1"/>
@@ -4002,15 +4024,15 @@
     <row r="26" spans="2:8" ht="14.25" customHeight="1"/>
     <row r="27" spans="2:8" ht="14.25" customHeight="1"/>
     <row r="28" spans="2:8" ht="14.25" customHeight="1">
-      <c r="C28" s="38" t="s">
+      <c r="C28" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="D28" s="38"/>
-      <c r="E28" s="38"/>
-      <c r="F28" s="38" t="s">
+      <c r="D28" s="45"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="G28" s="38"/>
+      <c r="G28" s="45"/>
     </row>
     <row r="29" spans="2:8" ht="14.25" customHeight="1">
       <c r="C29" s="3" t="s">
@@ -4045,11 +4067,11 @@
     </row>
     <row r="32" spans="2:8" ht="14.25" customHeight="1"/>
     <row r="33" spans="3:20" ht="14.25" customHeight="1">
-      <c r="C33" s="39"/>
-      <c r="D33" s="39"/>
-      <c r="E33" s="39"/>
-      <c r="F33" s="39"/>
-      <c r="G33" s="39"/>
+      <c r="C33" s="46"/>
+      <c r="D33" s="46"/>
+      <c r="E33" s="46"/>
+      <c r="F33" s="46"/>
+      <c r="G33" s="46"/>
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
     </row>
@@ -4096,7 +4118,7 @@
       <c r="Q38" s="15"/>
       <c r="R38" s="14"/>
       <c r="S38" s="16"/>
-      <c r="T38" s="37"/>
+      <c r="T38" s="44"/>
     </row>
     <row r="39" spans="3:20" ht="14.25" customHeight="1">
       <c r="K39" s="17"/>
@@ -4108,7 +4130,7 @@
       <c r="Q39" s="8"/>
       <c r="R39" s="14"/>
       <c r="S39" s="19"/>
-      <c r="T39" s="40"/>
+      <c r="T39" s="47"/>
     </row>
     <row r="40" spans="3:20" ht="14.25" customHeight="1"/>
     <row r="41" spans="3:20" ht="14.25" customHeight="1">
@@ -4132,7 +4154,7 @@
       <c r="Q42" s="15"/>
       <c r="R42" s="14"/>
       <c r="S42" s="16"/>
-      <c r="T42" s="37"/>
+      <c r="T42" s="44"/>
     </row>
     <row r="43" spans="3:20" s="8" customFormat="1" ht="14.25" customHeight="1">
       <c r="K43" s="17"/>
@@ -4140,7 +4162,7 @@
       <c r="N43" s="12"/>
       <c r="R43" s="14"/>
       <c r="S43" s="19"/>
-      <c r="T43" s="37"/>
+      <c r="T43" s="44"/>
     </row>
     <row r="44" spans="3:20" s="8" customFormat="1" ht="14.25" customHeight="1">
       <c r="K44" s="1"/>
@@ -4176,7 +4198,7 @@
       <c r="Q46" s="15"/>
       <c r="R46" s="14"/>
       <c r="S46" s="16"/>
-      <c r="T46" s="37"/>
+      <c r="T46" s="44"/>
     </row>
     <row r="47" spans="3:20" ht="14.25" customHeight="1">
       <c r="K47" s="17"/>
@@ -4188,7 +4210,7 @@
       <c r="Q47" s="8"/>
       <c r="R47" s="14"/>
       <c r="S47" s="19"/>
-      <c r="T47" s="37"/>
+      <c r="T47" s="44"/>
     </row>
     <row r="48" spans="3:20" ht="14.25" customHeight="1"/>
     <row r="49" spans="11:20" ht="14.25" customHeight="1">
@@ -4213,7 +4235,7 @@
       <c r="Q50" s="15"/>
       <c r="R50" s="14"/>
       <c r="S50" s="16"/>
-      <c r="T50" s="37"/>
+      <c r="T50" s="44"/>
     </row>
     <row r="51" spans="11:20" ht="14.25" customHeight="1">
       <c r="K51" s="17"/>
@@ -4225,7 +4247,7 @@
       <c r="Q51" s="8"/>
       <c r="R51" s="14"/>
       <c r="S51" s="19"/>
-      <c r="T51" s="37"/>
+      <c r="T51" s="44"/>
     </row>
     <row r="52" spans="11:20" ht="14.25" customHeight="1"/>
     <row r="53" spans="11:20" ht="14.25" customHeight="1">
@@ -4250,7 +4272,7 @@
       <c r="Q54" s="15"/>
       <c r="R54" s="14"/>
       <c r="S54" s="16"/>
-      <c r="T54" s="37"/>
+      <c r="T54" s="44"/>
     </row>
     <row r="55" spans="11:20">
       <c r="K55" s="17"/>
@@ -4262,7 +4284,7 @@
       <c r="Q55" s="8"/>
       <c r="R55" s="14"/>
       <c r="S55" s="19"/>
-      <c r="T55" s="40"/>
+      <c r="T55" s="47"/>
     </row>
     <row r="57" spans="11:20">
       <c r="K57" s="11"/>
@@ -4286,7 +4308,7 @@
       <c r="Q58" s="15"/>
       <c r="R58" s="14"/>
       <c r="S58" s="16"/>
-      <c r="T58" s="37"/>
+      <c r="T58" s="44"/>
     </row>
     <row r="59" spans="11:20">
       <c r="K59" s="17"/>
@@ -4298,7 +4320,7 @@
       <c r="Q59" s="8"/>
       <c r="R59" s="14"/>
       <c r="S59" s="19"/>
-      <c r="T59" s="40"/>
+      <c r="T59" s="47"/>
     </row>
     <row r="61" spans="11:20">
       <c r="K61" s="11"/>
@@ -4322,7 +4344,7 @@
       <c r="Q62" s="15"/>
       <c r="R62" s="14"/>
       <c r="S62" s="16"/>
-      <c r="T62" s="37"/>
+      <c r="T62" s="44"/>
     </row>
     <row r="63" spans="11:20">
       <c r="K63" s="17"/>
@@ -4334,7 +4356,7 @@
       <c r="Q63" s="8"/>
       <c r="R63" s="14"/>
       <c r="S63" s="19"/>
-      <c r="T63" s="40"/>
+      <c r="T63" s="47"/>
     </row>
     <row r="65" spans="11:20">
       <c r="K65" s="11"/>
@@ -4358,7 +4380,7 @@
       <c r="Q66" s="15"/>
       <c r="R66" s="14"/>
       <c r="S66" s="16"/>
-      <c r="T66" s="37"/>
+      <c r="T66" s="44"/>
     </row>
     <row r="67" spans="11:20">
       <c r="K67" s="17"/>
@@ -4370,7 +4392,7 @@
       <c r="Q67" s="8"/>
       <c r="R67" s="14"/>
       <c r="S67" s="19"/>
-      <c r="T67" s="40"/>
+      <c r="T67" s="47"/>
     </row>
     <row r="69" spans="11:20">
       <c r="K69" s="11"/>
@@ -4394,7 +4416,7 @@
       <c r="Q70" s="15"/>
       <c r="R70" s="14"/>
       <c r="S70" s="16"/>
-      <c r="T70" s="37"/>
+      <c r="T70" s="44"/>
     </row>
     <row r="71" spans="11:20">
       <c r="K71" s="17"/>
@@ -4406,7 +4428,7 @@
       <c r="Q71" s="8"/>
       <c r="R71" s="14"/>
       <c r="S71" s="19"/>
-      <c r="T71" s="40"/>
+      <c r="T71" s="47"/>
     </row>
     <row r="73" spans="11:20">
       <c r="K73" s="11"/>
@@ -4430,7 +4452,7 @@
       <c r="Q74" s="15"/>
       <c r="R74" s="14"/>
       <c r="S74" s="16"/>
-      <c r="T74" s="37"/>
+      <c r="T74" s="44"/>
     </row>
     <row r="75" spans="11:20">
       <c r="K75" s="17"/>
@@ -4442,7 +4464,7 @@
       <c r="Q75" s="8"/>
       <c r="R75" s="14"/>
       <c r="S75" s="19"/>
-      <c r="T75" s="40"/>
+      <c r="T75" s="47"/>
     </row>
     <row r="77" spans="11:20">
       <c r="K77" s="11"/>
@@ -4466,7 +4488,7 @@
       <c r="Q78" s="15"/>
       <c r="R78" s="14"/>
       <c r="S78" s="16"/>
-      <c r="T78" s="37"/>
+      <c r="T78" s="44"/>
     </row>
     <row r="79" spans="11:20">
       <c r="K79" s="17"/>
@@ -4478,7 +4500,7 @@
       <c r="Q79" s="8"/>
       <c r="R79" s="14"/>
       <c r="S79" s="19"/>
-      <c r="T79" s="40"/>
+      <c r="T79" s="47"/>
     </row>
     <row r="81" spans="11:20">
       <c r="K81" s="11"/>
@@ -4502,7 +4524,7 @@
       <c r="Q82" s="15"/>
       <c r="R82" s="14"/>
       <c r="S82" s="16"/>
-      <c r="T82" s="37"/>
+      <c r="T82" s="44"/>
     </row>
     <row r="83" spans="11:20">
       <c r="K83" s="17"/>
@@ -4514,7 +4536,7 @@
       <c r="Q83" s="8"/>
       <c r="R83" s="14"/>
       <c r="S83" s="19"/>
-      <c r="T83" s="40"/>
+      <c r="T83" s="47"/>
     </row>
     <row r="85" spans="11:20">
       <c r="K85" s="11"/>
@@ -4538,7 +4560,7 @@
       <c r="Q86" s="15"/>
       <c r="R86" s="14"/>
       <c r="S86" s="16"/>
-      <c r="T86" s="37"/>
+      <c r="T86" s="44"/>
     </row>
     <row r="87" spans="11:20">
       <c r="K87" s="17"/>
@@ -4550,7 +4572,7 @@
       <c r="Q87" s="8"/>
       <c r="R87" s="14"/>
       <c r="S87" s="19"/>
-      <c r="T87" s="40"/>
+      <c r="T87" s="47"/>
     </row>
     <row r="89" spans="11:20">
       <c r="K89" s="11"/>
@@ -4574,7 +4596,7 @@
       <c r="Q90" s="15"/>
       <c r="R90" s="14"/>
       <c r="S90" s="16"/>
-      <c r="T90" s="37"/>
+      <c r="T90" s="44"/>
     </row>
     <row r="91" spans="11:20">
       <c r="K91" s="17"/>
@@ -4586,7 +4608,7 @@
       <c r="Q91" s="8"/>
       <c r="R91" s="14"/>
       <c r="S91" s="19"/>
-      <c r="T91" s="40"/>
+      <c r="T91" s="47"/>
     </row>
     <row r="93" spans="11:20">
       <c r="K93" s="11"/>
@@ -4610,7 +4632,7 @@
       <c r="Q94" s="15"/>
       <c r="R94" s="14"/>
       <c r="S94" s="16"/>
-      <c r="T94" s="37"/>
+      <c r="T94" s="44"/>
     </row>
     <row r="95" spans="11:20">
       <c r="K95" s="17"/>
@@ -4622,7 +4644,7 @@
       <c r="Q95" s="8"/>
       <c r="R95" s="14"/>
       <c r="S95" s="19"/>
-      <c r="T95" s="40"/>
+      <c r="T95" s="47"/>
     </row>
     <row r="97" spans="11:20">
       <c r="K97" s="11"/>
@@ -4646,7 +4668,7 @@
       <c r="Q98" s="15"/>
       <c r="R98" s="14"/>
       <c r="S98" s="16"/>
-      <c r="T98" s="37"/>
+      <c r="T98" s="44"/>
     </row>
     <row r="99" spans="11:20">
       <c r="K99" s="17"/>
@@ -4658,7 +4680,7 @@
       <c r="Q99" s="8"/>
       <c r="R99" s="14"/>
       <c r="S99" s="19"/>
-      <c r="T99" s="40"/>
+      <c r="T99" s="47"/>
     </row>
     <row r="101" spans="11:20">
       <c r="K101" s="11"/>
@@ -4682,7 +4704,7 @@
       <c r="Q102" s="15"/>
       <c r="R102" s="14"/>
       <c r="S102" s="16"/>
-      <c r="T102" s="37"/>
+      <c r="T102" s="44"/>
     </row>
     <row r="103" spans="11:20">
       <c r="K103" s="17"/>
@@ -4694,7 +4716,7 @@
       <c r="Q103" s="8"/>
       <c r="R103" s="14"/>
       <c r="S103" s="19"/>
-      <c r="T103" s="40"/>
+      <c r="T103" s="47"/>
     </row>
     <row r="105" spans="11:20">
       <c r="K105" s="11"/>
@@ -4718,7 +4740,7 @@
       <c r="Q106" s="15"/>
       <c r="R106" s="14"/>
       <c r="S106" s="16"/>
-      <c r="T106" s="37"/>
+      <c r="T106" s="44"/>
     </row>
     <row r="107" spans="11:20">
       <c r="K107" s="17"/>
@@ -4730,7 +4752,7 @@
       <c r="Q107" s="8"/>
       <c r="R107" s="14"/>
       <c r="S107" s="19"/>
-      <c r="T107" s="40"/>
+      <c r="T107" s="47"/>
     </row>
     <row r="109" spans="11:20">
       <c r="K109" s="11"/>
@@ -4754,7 +4776,7 @@
       <c r="Q110" s="15"/>
       <c r="R110" s="14"/>
       <c r="S110" s="16"/>
-      <c r="T110" s="37"/>
+      <c r="T110" s="44"/>
     </row>
     <row r="111" spans="11:20">
       <c r="K111" s="17"/>
@@ -4766,7 +4788,7 @@
       <c r="Q111" s="8"/>
       <c r="R111" s="14"/>
       <c r="S111" s="19"/>
-      <c r="T111" s="40"/>
+      <c r="T111" s="47"/>
     </row>
     <row r="113" spans="11:20">
       <c r="K113" s="11"/>
@@ -4790,7 +4812,7 @@
       <c r="Q114" s="15"/>
       <c r="R114" s="14"/>
       <c r="S114" s="16"/>
-      <c r="T114" s="37"/>
+      <c r="T114" s="44"/>
     </row>
     <row r="115" spans="11:20">
       <c r="K115" s="17"/>
@@ -4802,7 +4824,7 @@
       <c r="Q115" s="8"/>
       <c r="R115" s="14"/>
       <c r="S115" s="19"/>
-      <c r="T115" s="40"/>
+      <c r="T115" s="47"/>
     </row>
     <row r="117" spans="11:20">
       <c r="K117" s="11"/>
@@ -4826,7 +4848,7 @@
       <c r="Q118" s="15"/>
       <c r="R118" s="14"/>
       <c r="S118" s="16"/>
-      <c r="T118" s="37"/>
+      <c r="T118" s="44"/>
     </row>
     <row r="119" spans="11:20">
       <c r="K119" s="17"/>
@@ -4838,7 +4860,7 @@
       <c r="Q119" s="8"/>
       <c r="R119" s="14"/>
       <c r="S119" s="19"/>
-      <c r="T119" s="40"/>
+      <c r="T119" s="47"/>
     </row>
     <row r="121" spans="11:20">
       <c r="K121" s="11"/>
@@ -4862,7 +4884,7 @@
       <c r="Q122" s="15"/>
       <c r="R122" s="14"/>
       <c r="S122" s="16"/>
-      <c r="T122" s="37"/>
+      <c r="T122" s="44"/>
     </row>
     <row r="123" spans="11:20">
       <c r="K123" s="17"/>
@@ -4874,7 +4896,7 @@
       <c r="Q123" s="8"/>
       <c r="R123" s="14"/>
       <c r="S123" s="19"/>
-      <c r="T123" s="40"/>
+      <c r="T123" s="47"/>
     </row>
   </sheetData>
   <mergeCells count="27">
@@ -4927,1890 +4949,1890 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:53" ht="12" customHeight="1">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="89" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
-      <c r="H1" s="82"/>
-      <c r="I1" s="65" t="s">
+      <c r="B1" s="89"/>
+      <c r="C1" s="89"/>
+      <c r="D1" s="89"/>
+      <c r="E1" s="89"/>
+      <c r="F1" s="89"/>
+      <c r="G1" s="89"/>
+      <c r="H1" s="89"/>
+      <c r="I1" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="80" t="s">
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
+      <c r="L1" s="72"/>
+      <c r="M1" s="87" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="80"/>
-      <c r="O1" s="80"/>
-      <c r="P1" s="80"/>
-      <c r="Q1" s="80"/>
-      <c r="R1" s="80"/>
-      <c r="S1" s="80"/>
-      <c r="T1" s="80"/>
-      <c r="U1" s="80"/>
-      <c r="V1" s="80"/>
-      <c r="W1" s="80"/>
-      <c r="X1" s="65" t="s">
+      <c r="N1" s="87"/>
+      <c r="O1" s="87"/>
+      <c r="P1" s="87"/>
+      <c r="Q1" s="87"/>
+      <c r="R1" s="87"/>
+      <c r="S1" s="87"/>
+      <c r="T1" s="87"/>
+      <c r="U1" s="87"/>
+      <c r="V1" s="87"/>
+      <c r="W1" s="87"/>
+      <c r="X1" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="Y1" s="65"/>
-      <c r="Z1" s="65"/>
-      <c r="AA1" s="84" t="s">
+      <c r="Y1" s="72"/>
+      <c r="Z1" s="72"/>
+      <c r="AA1" s="91" t="s">
         <v>32</v>
       </c>
-      <c r="AB1" s="84"/>
-      <c r="AC1" s="84"/>
-      <c r="AD1" s="84"/>
-      <c r="AE1" s="84"/>
-      <c r="AF1" s="84"/>
-      <c r="AG1" s="84"/>
-      <c r="AH1" s="84"/>
-      <c r="AI1" s="84"/>
-      <c r="AJ1" s="84"/>
-      <c r="AK1" s="69" t="s">
+      <c r="AB1" s="91"/>
+      <c r="AC1" s="91"/>
+      <c r="AD1" s="91"/>
+      <c r="AE1" s="91"/>
+      <c r="AF1" s="91"/>
+      <c r="AG1" s="91"/>
+      <c r="AH1" s="91"/>
+      <c r="AI1" s="91"/>
+      <c r="AJ1" s="91"/>
+      <c r="AK1" s="76" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="69"/>
-      <c r="AM1" s="69"/>
-      <c r="AN1" s="70" t="s">
+      <c r="AL1" s="76"/>
+      <c r="AM1" s="76"/>
+      <c r="AN1" s="77" t="s">
         <v>35</v>
       </c>
-      <c r="AO1" s="70"/>
-      <c r="AP1" s="70"/>
-      <c r="AQ1" s="69" t="s">
+      <c r="AO1" s="77"/>
+      <c r="AP1" s="77"/>
+      <c r="AQ1" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="AR1" s="69"/>
-      <c r="AS1" s="69"/>
-      <c r="AT1" s="72">
+      <c r="AR1" s="76"/>
+      <c r="AS1" s="76"/>
+      <c r="AT1" s="79">
         <f>AL7</f>
         <v>46195</v>
       </c>
-      <c r="AU1" s="72"/>
-      <c r="AV1" s="72"/>
-      <c r="AW1" s="72"/>
-      <c r="AX1" s="61" t="s">
+      <c r="AU1" s="79"/>
+      <c r="AV1" s="79"/>
+      <c r="AW1" s="79"/>
+      <c r="AX1" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="AY1" s="62"/>
-      <c r="AZ1" s="62"/>
-      <c r="BA1" s="63"/>
+      <c r="AY1" s="69"/>
+      <c r="AZ1" s="69"/>
+      <c r="BA1" s="70"/>
     </row>
     <row r="2" spans="1:53">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="71" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="64"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="64"/>
-      <c r="E2" s="64"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="65" t="s">
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="72" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-      <c r="L2" s="65"/>
-      <c r="M2" s="66" t="s">
+      <c r="J2" s="72"/>
+      <c r="K2" s="72"/>
+      <c r="L2" s="72"/>
+      <c r="M2" s="73" t="s">
         <v>29</v>
       </c>
-      <c r="N2" s="67"/>
-      <c r="O2" s="67"/>
-      <c r="P2" s="67"/>
-      <c r="Q2" s="67"/>
-      <c r="R2" s="67"/>
-      <c r="S2" s="67"/>
-      <c r="T2" s="67"/>
-      <c r="U2" s="67"/>
-      <c r="V2" s="67"/>
-      <c r="W2" s="68"/>
-      <c r="X2" s="65"/>
-      <c r="Y2" s="65"/>
-      <c r="Z2" s="65"/>
-      <c r="AA2" s="84"/>
-      <c r="AB2" s="84"/>
-      <c r="AC2" s="84"/>
-      <c r="AD2" s="84"/>
-      <c r="AE2" s="84"/>
-      <c r="AF2" s="84"/>
-      <c r="AG2" s="84"/>
-      <c r="AH2" s="84"/>
-      <c r="AI2" s="84"/>
-      <c r="AJ2" s="84"/>
-      <c r="AK2" s="69" t="s">
+      <c r="N2" s="74"/>
+      <c r="O2" s="74"/>
+      <c r="P2" s="74"/>
+      <c r="Q2" s="74"/>
+      <c r="R2" s="74"/>
+      <c r="S2" s="74"/>
+      <c r="T2" s="74"/>
+      <c r="U2" s="74"/>
+      <c r="V2" s="74"/>
+      <c r="W2" s="75"/>
+      <c r="X2" s="72"/>
+      <c r="Y2" s="72"/>
+      <c r="Z2" s="72"/>
+      <c r="AA2" s="91"/>
+      <c r="AB2" s="91"/>
+      <c r="AC2" s="91"/>
+      <c r="AD2" s="91"/>
+      <c r="AE2" s="91"/>
+      <c r="AF2" s="91"/>
+      <c r="AG2" s="91"/>
+      <c r="AH2" s="91"/>
+      <c r="AI2" s="91"/>
+      <c r="AJ2" s="91"/>
+      <c r="AK2" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="AL2" s="69"/>
-      <c r="AM2" s="69"/>
-      <c r="AN2" s="70"/>
-      <c r="AO2" s="70"/>
-      <c r="AP2" s="70"/>
-      <c r="AQ2" s="69" t="s">
+      <c r="AL2" s="76"/>
+      <c r="AM2" s="76"/>
+      <c r="AN2" s="77"/>
+      <c r="AO2" s="77"/>
+      <c r="AP2" s="77"/>
+      <c r="AQ2" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="AR2" s="69"/>
-      <c r="AS2" s="69"/>
-      <c r="AT2" s="72"/>
-      <c r="AU2" s="72"/>
-      <c r="AV2" s="72"/>
-      <c r="AW2" s="72"/>
-      <c r="AX2" s="73" t="s">
+      <c r="AR2" s="76"/>
+      <c r="AS2" s="76"/>
+      <c r="AT2" s="79"/>
+      <c r="AU2" s="79"/>
+      <c r="AV2" s="79"/>
+      <c r="AW2" s="79"/>
+      <c r="AX2" s="80" t="s">
         <v>27</v>
       </c>
-      <c r="AY2" s="74"/>
-      <c r="AZ2" s="74"/>
-      <c r="BA2" s="75"/>
+      <c r="AY2" s="81"/>
+      <c r="AZ2" s="81"/>
+      <c r="BA2" s="82"/>
     </row>
     <row r="3" spans="1:53" ht="12" customHeight="1">
-      <c r="A3" s="79" t="s">
+      <c r="A3" s="86" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="79"/>
-      <c r="C3" s="79"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="65" t="s">
+      <c r="B3" s="86"/>
+      <c r="C3" s="86"/>
+      <c r="D3" s="86"/>
+      <c r="E3" s="86"/>
+      <c r="F3" s="86"/>
+      <c r="G3" s="86"/>
+      <c r="H3" s="86"/>
+      <c r="I3" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="65"/>
-      <c r="K3" s="65"/>
-      <c r="L3" s="65"/>
-      <c r="M3" s="80"/>
-      <c r="N3" s="80"/>
-      <c r="O3" s="80"/>
-      <c r="P3" s="80"/>
-      <c r="Q3" s="80"/>
-      <c r="R3" s="80"/>
-      <c r="S3" s="80"/>
-      <c r="T3" s="80"/>
-      <c r="U3" s="80"/>
-      <c r="V3" s="80"/>
-      <c r="W3" s="80"/>
-      <c r="X3" s="65" t="s">
+      <c r="J3" s="72"/>
+      <c r="K3" s="72"/>
+      <c r="L3" s="72"/>
+      <c r="M3" s="87"/>
+      <c r="N3" s="87"/>
+      <c r="O3" s="87"/>
+      <c r="P3" s="87"/>
+      <c r="Q3" s="87"/>
+      <c r="R3" s="87"/>
+      <c r="S3" s="87"/>
+      <c r="T3" s="87"/>
+      <c r="U3" s="87"/>
+      <c r="V3" s="87"/>
+      <c r="W3" s="87"/>
+      <c r="X3" s="72" t="s">
         <v>25</v>
       </c>
-      <c r="Y3" s="65"/>
-      <c r="Z3" s="65"/>
-      <c r="AA3" s="81" t="s">
+      <c r="Y3" s="72"/>
+      <c r="Z3" s="72"/>
+      <c r="AA3" s="88" t="s">
         <v>33</v>
       </c>
-      <c r="AB3" s="81"/>
-      <c r="AC3" s="81"/>
-      <c r="AD3" s="81"/>
-      <c r="AE3" s="81"/>
-      <c r="AF3" s="81"/>
-      <c r="AG3" s="81"/>
-      <c r="AH3" s="81"/>
-      <c r="AI3" s="81"/>
-      <c r="AJ3" s="81"/>
-      <c r="AK3" s="81"/>
-      <c r="AL3" s="81"/>
-      <c r="AM3" s="81"/>
-      <c r="AN3" s="81"/>
-      <c r="AO3" s="81"/>
-      <c r="AP3" s="81"/>
-      <c r="AQ3" s="69" t="s">
+      <c r="AB3" s="88"/>
+      <c r="AC3" s="88"/>
+      <c r="AD3" s="88"/>
+      <c r="AE3" s="88"/>
+      <c r="AF3" s="88"/>
+      <c r="AG3" s="88"/>
+      <c r="AH3" s="88"/>
+      <c r="AI3" s="88"/>
+      <c r="AJ3" s="88"/>
+      <c r="AK3" s="88"/>
+      <c r="AL3" s="88"/>
+      <c r="AM3" s="88"/>
+      <c r="AN3" s="88"/>
+      <c r="AO3" s="88"/>
+      <c r="AP3" s="88"/>
+      <c r="AQ3" s="76" t="s">
         <v>15</v>
       </c>
-      <c r="AR3" s="69"/>
-      <c r="AS3" s="69"/>
-      <c r="AT3" s="85" t="str">
+      <c r="AR3" s="76"/>
+      <c r="AS3" s="76"/>
+      <c r="AT3" s="92" t="str">
         <f ca="1">INDIRECT("A" &amp; COUNTA(A7:A39) + 6)</f>
         <v>1.0</v>
       </c>
-      <c r="AU3" s="85"/>
-      <c r="AV3" s="85"/>
-      <c r="AW3" s="85"/>
-      <c r="AX3" s="76"/>
-      <c r="AY3" s="77"/>
-      <c r="AZ3" s="77"/>
-      <c r="BA3" s="78"/>
+      <c r="AU3" s="92"/>
+      <c r="AV3" s="92"/>
+      <c r="AW3" s="92"/>
+      <c r="AX3" s="83"/>
+      <c r="AY3" s="84"/>
+      <c r="AZ3" s="84"/>
+      <c r="BA3" s="85"/>
     </row>
     <row r="4" spans="1:53" ht="5.85" customHeight="1"/>
     <row r="5" spans="1:53" ht="14.25">
-      <c r="A5" s="83" t="s">
+      <c r="A5" s="90" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="83"/>
-      <c r="C5" s="83"/>
-      <c r="D5" s="83"/>
-      <c r="E5" s="83"/>
-      <c r="F5" s="83"/>
-      <c r="G5" s="83"/>
-      <c r="H5" s="83"/>
-      <c r="I5" s="83"/>
-      <c r="J5" s="83"/>
-      <c r="K5" s="83"/>
-      <c r="L5" s="83"/>
-      <c r="M5" s="83"/>
-      <c r="N5" s="83"/>
-      <c r="O5" s="83"/>
-      <c r="P5" s="83"/>
-      <c r="Q5" s="83"/>
-      <c r="R5" s="83"/>
-      <c r="S5" s="83"/>
-      <c r="T5" s="83"/>
-      <c r="U5" s="83"/>
-      <c r="V5" s="83"/>
-      <c r="W5" s="83"/>
-      <c r="X5" s="83"/>
-      <c r="Y5" s="83"/>
-      <c r="Z5" s="83"/>
-      <c r="AA5" s="83"/>
-      <c r="AB5" s="83"/>
-      <c r="AC5" s="83"/>
-      <c r="AD5" s="83"/>
-      <c r="AE5" s="83"/>
-      <c r="AF5" s="83"/>
-      <c r="AG5" s="83"/>
-      <c r="AH5" s="83"/>
-      <c r="AI5" s="83"/>
-      <c r="AJ5" s="83"/>
-      <c r="AK5" s="83"/>
-      <c r="AL5" s="83"/>
-      <c r="AM5" s="83"/>
-      <c r="AN5" s="83"/>
-      <c r="AO5" s="83"/>
-      <c r="AP5" s="83"/>
-      <c r="AQ5" s="83"/>
-      <c r="AR5" s="83"/>
-      <c r="AS5" s="83"/>
-      <c r="AT5" s="83"/>
-      <c r="AU5" s="83"/>
-      <c r="AV5" s="83"/>
-      <c r="AW5" s="83"/>
-      <c r="AX5" s="83"/>
-      <c r="AY5" s="83"/>
-      <c r="AZ5" s="83"/>
-      <c r="BA5" s="83"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
+      <c r="K5" s="90"/>
+      <c r="L5" s="90"/>
+      <c r="M5" s="90"/>
+      <c r="N5" s="90"/>
+      <c r="O5" s="90"/>
+      <c r="P5" s="90"/>
+      <c r="Q5" s="90"/>
+      <c r="R5" s="90"/>
+      <c r="S5" s="90"/>
+      <c r="T5" s="90"/>
+      <c r="U5" s="90"/>
+      <c r="V5" s="90"/>
+      <c r="W5" s="90"/>
+      <c r="X5" s="90"/>
+      <c r="Y5" s="90"/>
+      <c r="Z5" s="90"/>
+      <c r="AA5" s="90"/>
+      <c r="AB5" s="90"/>
+      <c r="AC5" s="90"/>
+      <c r="AD5" s="90"/>
+      <c r="AE5" s="90"/>
+      <c r="AF5" s="90"/>
+      <c r="AG5" s="90"/>
+      <c r="AH5" s="90"/>
+      <c r="AI5" s="90"/>
+      <c r="AJ5" s="90"/>
+      <c r="AK5" s="90"/>
+      <c r="AL5" s="90"/>
+      <c r="AM5" s="90"/>
+      <c r="AN5" s="90"/>
+      <c r="AO5" s="90"/>
+      <c r="AP5" s="90"/>
+      <c r="AQ5" s="90"/>
+      <c r="AR5" s="90"/>
+      <c r="AS5" s="90"/>
+      <c r="AT5" s="90"/>
+      <c r="AU5" s="90"/>
+      <c r="AV5" s="90"/>
+      <c r="AW5" s="90"/>
+      <c r="AX5" s="90"/>
+      <c r="AY5" s="90"/>
+      <c r="AZ5" s="90"/>
+      <c r="BA5" s="90"/>
     </row>
     <row r="6" spans="1:53">
-      <c r="A6" s="86" t="s">
+      <c r="A6" s="93" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="87"/>
-      <c r="C6" s="71" t="s">
+      <c r="B6" s="94"/>
+      <c r="C6" s="78" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="71"/>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
-      <c r="G6" s="71"/>
-      <c r="H6" s="71"/>
-      <c r="I6" s="71"/>
-      <c r="J6" s="71"/>
-      <c r="K6" s="71"/>
-      <c r="L6" s="71"/>
-      <c r="M6" s="71"/>
-      <c r="N6" s="71"/>
-      <c r="O6" s="71"/>
-      <c r="P6" s="71"/>
-      <c r="Q6" s="71" t="s">
+      <c r="D6" s="78"/>
+      <c r="E6" s="78"/>
+      <c r="F6" s="78"/>
+      <c r="G6" s="78"/>
+      <c r="H6" s="78"/>
+      <c r="I6" s="78"/>
+      <c r="J6" s="78"/>
+      <c r="K6" s="78"/>
+      <c r="L6" s="78"/>
+      <c r="M6" s="78"/>
+      <c r="N6" s="78"/>
+      <c r="O6" s="78"/>
+      <c r="P6" s="78"/>
+      <c r="Q6" s="78" t="s">
         <v>30</v>
       </c>
-      <c r="R6" s="71"/>
-      <c r="S6" s="71"/>
-      <c r="T6" s="71"/>
-      <c r="U6" s="71"/>
-      <c r="V6" s="71"/>
-      <c r="W6" s="71"/>
-      <c r="X6" s="71"/>
-      <c r="Y6" s="71"/>
-      <c r="Z6" s="71"/>
-      <c r="AA6" s="71"/>
-      <c r="AB6" s="71"/>
-      <c r="AC6" s="71"/>
-      <c r="AD6" s="71"/>
-      <c r="AE6" s="71"/>
-      <c r="AF6" s="71"/>
-      <c r="AG6" s="71"/>
-      <c r="AH6" s="71"/>
-      <c r="AI6" s="71"/>
-      <c r="AJ6" s="71"/>
-      <c r="AK6" s="71"/>
-      <c r="AL6" s="71" t="s">
+      <c r="R6" s="78"/>
+      <c r="S6" s="78"/>
+      <c r="T6" s="78"/>
+      <c r="U6" s="78"/>
+      <c r="V6" s="78"/>
+      <c r="W6" s="78"/>
+      <c r="X6" s="78"/>
+      <c r="Y6" s="78"/>
+      <c r="Z6" s="78"/>
+      <c r="AA6" s="78"/>
+      <c r="AB6" s="78"/>
+      <c r="AC6" s="78"/>
+      <c r="AD6" s="78"/>
+      <c r="AE6" s="78"/>
+      <c r="AF6" s="78"/>
+      <c r="AG6" s="78"/>
+      <c r="AH6" s="78"/>
+      <c r="AI6" s="78"/>
+      <c r="AJ6" s="78"/>
+      <c r="AK6" s="78"/>
+      <c r="AL6" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="AM6" s="71"/>
-      <c r="AN6" s="71"/>
-      <c r="AO6" s="71"/>
-      <c r="AP6" s="71" t="s">
+      <c r="AM6" s="78"/>
+      <c r="AN6" s="78"/>
+      <c r="AO6" s="78"/>
+      <c r="AP6" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="AQ6" s="71"/>
-      <c r="AR6" s="71"/>
-      <c r="AS6" s="71" t="s">
+      <c r="AQ6" s="78"/>
+      <c r="AR6" s="78"/>
+      <c r="AS6" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="AT6" s="71"/>
-      <c r="AU6" s="71"/>
-      <c r="AV6" s="71" t="s">
+      <c r="AT6" s="78"/>
+      <c r="AU6" s="78"/>
+      <c r="AV6" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="AW6" s="71"/>
-      <c r="AX6" s="71"/>
-      <c r="AY6" s="71"/>
-      <c r="AZ6" s="71"/>
-      <c r="BA6" s="71"/>
+      <c r="AW6" s="78"/>
+      <c r="AX6" s="78"/>
+      <c r="AY6" s="78"/>
+      <c r="AZ6" s="78"/>
+      <c r="BA6" s="78"/>
     </row>
     <row r="7" spans="1:53">
-      <c r="A7" s="59" t="s">
+      <c r="A7" s="66" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="42"/>
-      <c r="C7" s="43" t="s">
+      <c r="B7" s="49"/>
+      <c r="C7" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="43"/>
-      <c r="E7" s="43"/>
-      <c r="F7" s="43"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="43"/>
-      <c r="I7" s="43"/>
-      <c r="J7" s="43"/>
-      <c r="K7" s="43"/>
-      <c r="L7" s="43"/>
-      <c r="M7" s="43"/>
-      <c r="N7" s="43"/>
-      <c r="O7" s="43"/>
-      <c r="P7" s="43"/>
-      <c r="Q7" s="43"/>
-      <c r="R7" s="43"/>
-      <c r="S7" s="43"/>
-      <c r="T7" s="43"/>
-      <c r="U7" s="43"/>
-      <c r="V7" s="43"/>
-      <c r="W7" s="43"/>
-      <c r="X7" s="43"/>
-      <c r="Y7" s="43"/>
-      <c r="Z7" s="43"/>
-      <c r="AA7" s="43"/>
-      <c r="AB7" s="43"/>
-      <c r="AC7" s="43"/>
-      <c r="AD7" s="43"/>
-      <c r="AE7" s="43"/>
-      <c r="AF7" s="43"/>
-      <c r="AG7" s="43"/>
-      <c r="AH7" s="43"/>
-      <c r="AI7" s="43"/>
-      <c r="AJ7" s="43"/>
-      <c r="AK7" s="43"/>
-      <c r="AL7" s="47">
+      <c r="D7" s="50"/>
+      <c r="E7" s="50"/>
+      <c r="F7" s="50"/>
+      <c r="G7" s="50"/>
+      <c r="H7" s="50"/>
+      <c r="I7" s="50"/>
+      <c r="J7" s="50"/>
+      <c r="K7" s="50"/>
+      <c r="L7" s="50"/>
+      <c r="M7" s="50"/>
+      <c r="N7" s="50"/>
+      <c r="O7" s="50"/>
+      <c r="P7" s="50"/>
+      <c r="Q7" s="50"/>
+      <c r="R7" s="50"/>
+      <c r="S7" s="50"/>
+      <c r="T7" s="50"/>
+      <c r="U7" s="50"/>
+      <c r="V7" s="50"/>
+      <c r="W7" s="50"/>
+      <c r="X7" s="50"/>
+      <c r="Y7" s="50"/>
+      <c r="Z7" s="50"/>
+      <c r="AA7" s="50"/>
+      <c r="AB7" s="50"/>
+      <c r="AC7" s="50"/>
+      <c r="AD7" s="50"/>
+      <c r="AE7" s="50"/>
+      <c r="AF7" s="50"/>
+      <c r="AG7" s="50"/>
+      <c r="AH7" s="50"/>
+      <c r="AI7" s="50"/>
+      <c r="AJ7" s="50"/>
+      <c r="AK7" s="50"/>
+      <c r="AL7" s="54">
         <v>46195</v>
       </c>
-      <c r="AM7" s="48"/>
-      <c r="AN7" s="48"/>
-      <c r="AO7" s="48"/>
-      <c r="AP7" s="43" t="s">
+      <c r="AM7" s="55"/>
+      <c r="AN7" s="55"/>
+      <c r="AO7" s="55"/>
+      <c r="AP7" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="AQ7" s="43"/>
-      <c r="AR7" s="43"/>
-      <c r="AS7" s="43"/>
-      <c r="AT7" s="43"/>
-      <c r="AU7" s="43"/>
-      <c r="AV7" s="43"/>
-      <c r="AW7" s="43"/>
-      <c r="AX7" s="43"/>
-      <c r="AY7" s="43"/>
-      <c r="AZ7" s="43"/>
-      <c r="BA7" s="43"/>
+      <c r="AQ7" s="50"/>
+      <c r="AR7" s="50"/>
+      <c r="AS7" s="50"/>
+      <c r="AT7" s="50"/>
+      <c r="AU7" s="50"/>
+      <c r="AV7" s="50"/>
+      <c r="AW7" s="50"/>
+      <c r="AX7" s="50"/>
+      <c r="AY7" s="50"/>
+      <c r="AZ7" s="50"/>
+      <c r="BA7" s="50"/>
     </row>
     <row r="8" spans="1:53">
-      <c r="A8" s="42"/>
-      <c r="B8" s="42"/>
-      <c r="C8" s="44"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="44"/>
-      <c r="F8" s="44"/>
-      <c r="G8" s="44"/>
-      <c r="H8" s="44"/>
-      <c r="I8" s="44"/>
-      <c r="J8" s="44"/>
-      <c r="K8" s="44"/>
-      <c r="L8" s="44"/>
-      <c r="M8" s="44"/>
-      <c r="N8" s="44"/>
-      <c r="O8" s="44"/>
-      <c r="P8" s="44"/>
-      <c r="Q8" s="54"/>
-      <c r="R8" s="55"/>
-      <c r="S8" s="55"/>
-      <c r="T8" s="55"/>
-      <c r="U8" s="55"/>
-      <c r="V8" s="55"/>
-      <c r="W8" s="55"/>
-      <c r="X8" s="55"/>
-      <c r="Y8" s="55"/>
-      <c r="Z8" s="55"/>
-      <c r="AA8" s="55"/>
-      <c r="AB8" s="55"/>
-      <c r="AC8" s="55"/>
-      <c r="AD8" s="55"/>
-      <c r="AE8" s="55"/>
-      <c r="AF8" s="55"/>
-      <c r="AG8" s="55"/>
-      <c r="AH8" s="55"/>
-      <c r="AI8" s="55"/>
-      <c r="AJ8" s="55"/>
-      <c r="AK8" s="56"/>
-      <c r="AL8" s="49"/>
-      <c r="AM8" s="50"/>
-      <c r="AN8" s="50"/>
-      <c r="AO8" s="51"/>
-      <c r="AP8" s="43"/>
-      <c r="AQ8" s="43"/>
-      <c r="AR8" s="43"/>
-      <c r="AS8" s="43"/>
-      <c r="AT8" s="43"/>
-      <c r="AU8" s="43"/>
-      <c r="AV8" s="43"/>
-      <c r="AW8" s="43"/>
-      <c r="AX8" s="43"/>
-      <c r="AY8" s="43"/>
-      <c r="AZ8" s="43"/>
-      <c r="BA8" s="43"/>
+      <c r="A8" s="49"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="51"/>
+      <c r="L8" s="51"/>
+      <c r="M8" s="51"/>
+      <c r="N8" s="51"/>
+      <c r="O8" s="51"/>
+      <c r="P8" s="51"/>
+      <c r="Q8" s="61"/>
+      <c r="R8" s="62"/>
+      <c r="S8" s="62"/>
+      <c r="T8" s="62"/>
+      <c r="U8" s="62"/>
+      <c r="V8" s="62"/>
+      <c r="W8" s="62"/>
+      <c r="X8" s="62"/>
+      <c r="Y8" s="62"/>
+      <c r="Z8" s="62"/>
+      <c r="AA8" s="62"/>
+      <c r="AB8" s="62"/>
+      <c r="AC8" s="62"/>
+      <c r="AD8" s="62"/>
+      <c r="AE8" s="62"/>
+      <c r="AF8" s="62"/>
+      <c r="AG8" s="62"/>
+      <c r="AH8" s="62"/>
+      <c r="AI8" s="62"/>
+      <c r="AJ8" s="62"/>
+      <c r="AK8" s="63"/>
+      <c r="AL8" s="56"/>
+      <c r="AM8" s="57"/>
+      <c r="AN8" s="57"/>
+      <c r="AO8" s="58"/>
+      <c r="AP8" s="50"/>
+      <c r="AQ8" s="50"/>
+      <c r="AR8" s="50"/>
+      <c r="AS8" s="50"/>
+      <c r="AT8" s="50"/>
+      <c r="AU8" s="50"/>
+      <c r="AV8" s="50"/>
+      <c r="AW8" s="50"/>
+      <c r="AX8" s="50"/>
+      <c r="AY8" s="50"/>
+      <c r="AZ8" s="50"/>
+      <c r="BA8" s="50"/>
     </row>
     <row r="9" spans="1:53">
-      <c r="A9" s="57"/>
-      <c r="B9" s="58"/>
-      <c r="C9" s="44"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="44"/>
-      <c r="F9" s="44"/>
-      <c r="G9" s="44"/>
-      <c r="H9" s="44"/>
-      <c r="I9" s="44"/>
-      <c r="J9" s="44"/>
-      <c r="K9" s="44"/>
-      <c r="L9" s="44"/>
-      <c r="M9" s="44"/>
-      <c r="N9" s="44"/>
-      <c r="O9" s="44"/>
-      <c r="P9" s="44"/>
-      <c r="Q9" s="54"/>
-      <c r="R9" s="55"/>
-      <c r="S9" s="55"/>
-      <c r="T9" s="55"/>
-      <c r="U9" s="55"/>
-      <c r="V9" s="55"/>
-      <c r="W9" s="55"/>
-      <c r="X9" s="55"/>
-      <c r="Y9" s="55"/>
-      <c r="Z9" s="55"/>
-      <c r="AA9" s="55"/>
-      <c r="AB9" s="55"/>
-      <c r="AC9" s="55"/>
-      <c r="AD9" s="55"/>
-      <c r="AE9" s="55"/>
-      <c r="AF9" s="55"/>
-      <c r="AG9" s="55"/>
-      <c r="AH9" s="55"/>
-      <c r="AI9" s="55"/>
-      <c r="AJ9" s="55"/>
-      <c r="AK9" s="56"/>
-      <c r="AL9" s="49"/>
-      <c r="AM9" s="50"/>
-      <c r="AN9" s="50"/>
-      <c r="AO9" s="51"/>
-      <c r="AP9" s="43"/>
-      <c r="AQ9" s="43"/>
-      <c r="AR9" s="43"/>
-      <c r="AS9" s="43"/>
-      <c r="AT9" s="43"/>
-      <c r="AU9" s="43"/>
-      <c r="AV9" s="43"/>
-      <c r="AW9" s="43"/>
-      <c r="AX9" s="43"/>
-      <c r="AY9" s="43"/>
-      <c r="AZ9" s="43"/>
-      <c r="BA9" s="43"/>
+      <c r="A9" s="64"/>
+      <c r="B9" s="65"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="51"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="51"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="51"/>
+      <c r="J9" s="51"/>
+      <c r="K9" s="51"/>
+      <c r="L9" s="51"/>
+      <c r="M9" s="51"/>
+      <c r="N9" s="51"/>
+      <c r="O9" s="51"/>
+      <c r="P9" s="51"/>
+      <c r="Q9" s="61"/>
+      <c r="R9" s="62"/>
+      <c r="S9" s="62"/>
+      <c r="T9" s="62"/>
+      <c r="U9" s="62"/>
+      <c r="V9" s="62"/>
+      <c r="W9" s="62"/>
+      <c r="X9" s="62"/>
+      <c r="Y9" s="62"/>
+      <c r="Z9" s="62"/>
+      <c r="AA9" s="62"/>
+      <c r="AB9" s="62"/>
+      <c r="AC9" s="62"/>
+      <c r="AD9" s="62"/>
+      <c r="AE9" s="62"/>
+      <c r="AF9" s="62"/>
+      <c r="AG9" s="62"/>
+      <c r="AH9" s="62"/>
+      <c r="AI9" s="62"/>
+      <c r="AJ9" s="62"/>
+      <c r="AK9" s="63"/>
+      <c r="AL9" s="56"/>
+      <c r="AM9" s="57"/>
+      <c r="AN9" s="57"/>
+      <c r="AO9" s="58"/>
+      <c r="AP9" s="50"/>
+      <c r="AQ9" s="50"/>
+      <c r="AR9" s="50"/>
+      <c r="AS9" s="50"/>
+      <c r="AT9" s="50"/>
+      <c r="AU9" s="50"/>
+      <c r="AV9" s="50"/>
+      <c r="AW9" s="50"/>
+      <c r="AX9" s="50"/>
+      <c r="AY9" s="50"/>
+      <c r="AZ9" s="50"/>
+      <c r="BA9" s="50"/>
     </row>
     <row r="10" spans="1:53">
-      <c r="A10" s="57"/>
-      <c r="B10" s="58"/>
-      <c r="C10" s="44"/>
-      <c r="D10" s="44"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
-      <c r="I10" s="44"/>
-      <c r="J10" s="44"/>
-      <c r="K10" s="44"/>
-      <c r="L10" s="44"/>
-      <c r="M10" s="44"/>
-      <c r="N10" s="44"/>
-      <c r="O10" s="44"/>
-      <c r="P10" s="44"/>
-      <c r="Q10" s="44"/>
-      <c r="R10" s="43"/>
-      <c r="S10" s="43"/>
-      <c r="T10" s="43"/>
-      <c r="U10" s="43"/>
-      <c r="V10" s="43"/>
-      <c r="W10" s="43"/>
-      <c r="X10" s="43"/>
-      <c r="Y10" s="43"/>
-      <c r="Z10" s="43"/>
-      <c r="AA10" s="43"/>
-      <c r="AB10" s="43"/>
-      <c r="AC10" s="43"/>
-      <c r="AD10" s="43"/>
-      <c r="AE10" s="43"/>
-      <c r="AF10" s="43"/>
-      <c r="AG10" s="43"/>
-      <c r="AH10" s="43"/>
-      <c r="AI10" s="43"/>
-      <c r="AJ10" s="43"/>
-      <c r="AK10" s="43"/>
-      <c r="AL10" s="41"/>
-      <c r="AM10" s="42"/>
-      <c r="AN10" s="42"/>
-      <c r="AO10" s="42"/>
-      <c r="AP10" s="43"/>
-      <c r="AQ10" s="43"/>
-      <c r="AR10" s="43"/>
-      <c r="AS10" s="43"/>
-      <c r="AT10" s="43"/>
-      <c r="AU10" s="43"/>
-      <c r="AV10" s="43"/>
-      <c r="AW10" s="43"/>
-      <c r="AX10" s="43"/>
-      <c r="AY10" s="43"/>
-      <c r="AZ10" s="43"/>
-      <c r="BA10" s="43"/>
+      <c r="A10" s="64"/>
+      <c r="B10" s="65"/>
+      <c r="C10" s="51"/>
+      <c r="D10" s="51"/>
+      <c r="E10" s="51"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="51"/>
+      <c r="K10" s="51"/>
+      <c r="L10" s="51"/>
+      <c r="M10" s="51"/>
+      <c r="N10" s="51"/>
+      <c r="O10" s="51"/>
+      <c r="P10" s="51"/>
+      <c r="Q10" s="51"/>
+      <c r="R10" s="50"/>
+      <c r="S10" s="50"/>
+      <c r="T10" s="50"/>
+      <c r="U10" s="50"/>
+      <c r="V10" s="50"/>
+      <c r="W10" s="50"/>
+      <c r="X10" s="50"/>
+      <c r="Y10" s="50"/>
+      <c r="Z10" s="50"/>
+      <c r="AA10" s="50"/>
+      <c r="AB10" s="50"/>
+      <c r="AC10" s="50"/>
+      <c r="AD10" s="50"/>
+      <c r="AE10" s="50"/>
+      <c r="AF10" s="50"/>
+      <c r="AG10" s="50"/>
+      <c r="AH10" s="50"/>
+      <c r="AI10" s="50"/>
+      <c r="AJ10" s="50"/>
+      <c r="AK10" s="50"/>
+      <c r="AL10" s="48"/>
+      <c r="AM10" s="49"/>
+      <c r="AN10" s="49"/>
+      <c r="AO10" s="49"/>
+      <c r="AP10" s="50"/>
+      <c r="AQ10" s="50"/>
+      <c r="AR10" s="50"/>
+      <c r="AS10" s="50"/>
+      <c r="AT10" s="50"/>
+      <c r="AU10" s="50"/>
+      <c r="AV10" s="50"/>
+      <c r="AW10" s="50"/>
+      <c r="AX10" s="50"/>
+      <c r="AY10" s="50"/>
+      <c r="AZ10" s="50"/>
+      <c r="BA10" s="50"/>
     </row>
     <row r="11" spans="1:53">
-      <c r="A11" s="57"/>
-      <c r="B11" s="58"/>
-      <c r="C11" s="44"/>
-      <c r="D11" s="44"/>
-      <c r="E11" s="44"/>
-      <c r="F11" s="44"/>
-      <c r="G11" s="44"/>
-      <c r="H11" s="44"/>
-      <c r="I11" s="44"/>
-      <c r="J11" s="44"/>
-      <c r="K11" s="44"/>
-      <c r="L11" s="44"/>
-      <c r="M11" s="44"/>
-      <c r="N11" s="44"/>
-      <c r="O11" s="44"/>
-      <c r="P11" s="44"/>
-      <c r="Q11" s="44"/>
-      <c r="R11" s="43"/>
-      <c r="S11" s="43"/>
-      <c r="T11" s="43"/>
-      <c r="U11" s="43"/>
-      <c r="V11" s="43"/>
-      <c r="W11" s="43"/>
-      <c r="X11" s="43"/>
-      <c r="Y11" s="43"/>
-      <c r="Z11" s="43"/>
-      <c r="AA11" s="43"/>
-      <c r="AB11" s="43"/>
-      <c r="AC11" s="43"/>
-      <c r="AD11" s="43"/>
-      <c r="AE11" s="43"/>
-      <c r="AF11" s="43"/>
-      <c r="AG11" s="43"/>
-      <c r="AH11" s="43"/>
-      <c r="AI11" s="43"/>
-      <c r="AJ11" s="43"/>
-      <c r="AK11" s="43"/>
-      <c r="AL11" s="41"/>
-      <c r="AM11" s="42"/>
-      <c r="AN11" s="42"/>
-      <c r="AO11" s="42"/>
-      <c r="AP11" s="43"/>
-      <c r="AQ11" s="43"/>
-      <c r="AR11" s="43"/>
-      <c r="AS11" s="43"/>
-      <c r="AT11" s="43"/>
-      <c r="AU11" s="43"/>
-      <c r="AV11" s="43"/>
-      <c r="AW11" s="43"/>
-      <c r="AX11" s="43"/>
-      <c r="AY11" s="43"/>
-      <c r="AZ11" s="43"/>
-      <c r="BA11" s="43"/>
+      <c r="A11" s="64"/>
+      <c r="B11" s="65"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="51"/>
+      <c r="K11" s="51"/>
+      <c r="L11" s="51"/>
+      <c r="M11" s="51"/>
+      <c r="N11" s="51"/>
+      <c r="O11" s="51"/>
+      <c r="P11" s="51"/>
+      <c r="Q11" s="51"/>
+      <c r="R11" s="50"/>
+      <c r="S11" s="50"/>
+      <c r="T11" s="50"/>
+      <c r="U11" s="50"/>
+      <c r="V11" s="50"/>
+      <c r="W11" s="50"/>
+      <c r="X11" s="50"/>
+      <c r="Y11" s="50"/>
+      <c r="Z11" s="50"/>
+      <c r="AA11" s="50"/>
+      <c r="AB11" s="50"/>
+      <c r="AC11" s="50"/>
+      <c r="AD11" s="50"/>
+      <c r="AE11" s="50"/>
+      <c r="AF11" s="50"/>
+      <c r="AG11" s="50"/>
+      <c r="AH11" s="50"/>
+      <c r="AI11" s="50"/>
+      <c r="AJ11" s="50"/>
+      <c r="AK11" s="50"/>
+      <c r="AL11" s="48"/>
+      <c r="AM11" s="49"/>
+      <c r="AN11" s="49"/>
+      <c r="AO11" s="49"/>
+      <c r="AP11" s="50"/>
+      <c r="AQ11" s="50"/>
+      <c r="AR11" s="50"/>
+      <c r="AS11" s="50"/>
+      <c r="AT11" s="50"/>
+      <c r="AU11" s="50"/>
+      <c r="AV11" s="50"/>
+      <c r="AW11" s="50"/>
+      <c r="AX11" s="50"/>
+      <c r="AY11" s="50"/>
+      <c r="AZ11" s="50"/>
+      <c r="BA11" s="50"/>
     </row>
     <row r="12" spans="1:53">
-      <c r="A12" s="42"/>
-      <c r="B12" s="42"/>
-      <c r="C12" s="44"/>
-      <c r="D12" s="44"/>
-      <c r="E12" s="44"/>
-      <c r="F12" s="44"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="44"/>
-      <c r="I12" s="44"/>
-      <c r="J12" s="44"/>
-      <c r="K12" s="44"/>
-      <c r="L12" s="44"/>
-      <c r="M12" s="44"/>
-      <c r="N12" s="44"/>
-      <c r="O12" s="44"/>
-      <c r="P12" s="44"/>
-      <c r="Q12" s="43"/>
-      <c r="R12" s="43"/>
-      <c r="S12" s="43"/>
-      <c r="T12" s="43"/>
-      <c r="U12" s="43"/>
-      <c r="V12" s="43"/>
-      <c r="W12" s="43"/>
-      <c r="X12" s="43"/>
-      <c r="Y12" s="43"/>
-      <c r="Z12" s="43"/>
-      <c r="AA12" s="43"/>
-      <c r="AB12" s="43"/>
-      <c r="AC12" s="43"/>
-      <c r="AD12" s="43"/>
-      <c r="AE12" s="43"/>
-      <c r="AF12" s="43"/>
-      <c r="AG12" s="43"/>
-      <c r="AH12" s="43"/>
-      <c r="AI12" s="43"/>
-      <c r="AJ12" s="43"/>
-      <c r="AK12" s="43"/>
-      <c r="AL12" s="41"/>
-      <c r="AM12" s="42"/>
-      <c r="AN12" s="42"/>
-      <c r="AO12" s="42"/>
-      <c r="AP12" s="43"/>
-      <c r="AQ12" s="43"/>
-      <c r="AR12" s="43"/>
-      <c r="AS12" s="43"/>
-      <c r="AT12" s="43"/>
-      <c r="AU12" s="43"/>
-      <c r="AV12" s="43"/>
-      <c r="AW12" s="43"/>
-      <c r="AX12" s="43"/>
-      <c r="AY12" s="43"/>
-      <c r="AZ12" s="43"/>
-      <c r="BA12" s="43"/>
+      <c r="A12" s="49"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="51"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="51"/>
+      <c r="J12" s="51"/>
+      <c r="K12" s="51"/>
+      <c r="L12" s="51"/>
+      <c r="M12" s="51"/>
+      <c r="N12" s="51"/>
+      <c r="O12" s="51"/>
+      <c r="P12" s="51"/>
+      <c r="Q12" s="50"/>
+      <c r="R12" s="50"/>
+      <c r="S12" s="50"/>
+      <c r="T12" s="50"/>
+      <c r="U12" s="50"/>
+      <c r="V12" s="50"/>
+      <c r="W12" s="50"/>
+      <c r="X12" s="50"/>
+      <c r="Y12" s="50"/>
+      <c r="Z12" s="50"/>
+      <c r="AA12" s="50"/>
+      <c r="AB12" s="50"/>
+      <c r="AC12" s="50"/>
+      <c r="AD12" s="50"/>
+      <c r="AE12" s="50"/>
+      <c r="AF12" s="50"/>
+      <c r="AG12" s="50"/>
+      <c r="AH12" s="50"/>
+      <c r="AI12" s="50"/>
+      <c r="AJ12" s="50"/>
+      <c r="AK12" s="50"/>
+      <c r="AL12" s="48"/>
+      <c r="AM12" s="49"/>
+      <c r="AN12" s="49"/>
+      <c r="AO12" s="49"/>
+      <c r="AP12" s="50"/>
+      <c r="AQ12" s="50"/>
+      <c r="AR12" s="50"/>
+      <c r="AS12" s="50"/>
+      <c r="AT12" s="50"/>
+      <c r="AU12" s="50"/>
+      <c r="AV12" s="50"/>
+      <c r="AW12" s="50"/>
+      <c r="AX12" s="50"/>
+      <c r="AY12" s="50"/>
+      <c r="AZ12" s="50"/>
+      <c r="BA12" s="50"/>
     </row>
     <row r="13" spans="1:53">
-      <c r="A13" s="53"/>
-      <c r="B13" s="53"/>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="45"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="45"/>
-      <c r="I13" s="45"/>
-      <c r="J13" s="45"/>
-      <c r="K13" s="45"/>
-      <c r="L13" s="45"/>
-      <c r="M13" s="45"/>
-      <c r="N13" s="45"/>
-      <c r="O13" s="45"/>
-      <c r="P13" s="45"/>
-      <c r="Q13" s="44"/>
-      <c r="R13" s="43"/>
-      <c r="S13" s="43"/>
-      <c r="T13" s="43"/>
-      <c r="U13" s="43"/>
-      <c r="V13" s="43"/>
-      <c r="W13" s="43"/>
-      <c r="X13" s="43"/>
-      <c r="Y13" s="43"/>
-      <c r="Z13" s="43"/>
-      <c r="AA13" s="43"/>
-      <c r="AB13" s="43"/>
-      <c r="AC13" s="43"/>
-      <c r="AD13" s="43"/>
-      <c r="AE13" s="43"/>
-      <c r="AF13" s="43"/>
-      <c r="AG13" s="43"/>
-      <c r="AH13" s="43"/>
-      <c r="AI13" s="43"/>
-      <c r="AJ13" s="43"/>
-      <c r="AK13" s="43"/>
-      <c r="AL13" s="52"/>
-      <c r="AM13" s="53"/>
-      <c r="AN13" s="53"/>
-      <c r="AO13" s="53"/>
-      <c r="AP13" s="43"/>
-      <c r="AQ13" s="43"/>
-      <c r="AR13" s="43"/>
-      <c r="AS13" s="45"/>
-      <c r="AT13" s="45"/>
-      <c r="AU13" s="45"/>
-      <c r="AV13" s="45"/>
-      <c r="AW13" s="45"/>
-      <c r="AX13" s="45"/>
-      <c r="AY13" s="45"/>
-      <c r="AZ13" s="45"/>
-      <c r="BA13" s="45"/>
+      <c r="A13" s="60"/>
+      <c r="B13" s="60"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="52"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="52"/>
+      <c r="I13" s="52"/>
+      <c r="J13" s="52"/>
+      <c r="K13" s="52"/>
+      <c r="L13" s="52"/>
+      <c r="M13" s="52"/>
+      <c r="N13" s="52"/>
+      <c r="O13" s="52"/>
+      <c r="P13" s="52"/>
+      <c r="Q13" s="51"/>
+      <c r="R13" s="50"/>
+      <c r="S13" s="50"/>
+      <c r="T13" s="50"/>
+      <c r="U13" s="50"/>
+      <c r="V13" s="50"/>
+      <c r="W13" s="50"/>
+      <c r="X13" s="50"/>
+      <c r="Y13" s="50"/>
+      <c r="Z13" s="50"/>
+      <c r="AA13" s="50"/>
+      <c r="AB13" s="50"/>
+      <c r="AC13" s="50"/>
+      <c r="AD13" s="50"/>
+      <c r="AE13" s="50"/>
+      <c r="AF13" s="50"/>
+      <c r="AG13" s="50"/>
+      <c r="AH13" s="50"/>
+      <c r="AI13" s="50"/>
+      <c r="AJ13" s="50"/>
+      <c r="AK13" s="50"/>
+      <c r="AL13" s="59"/>
+      <c r="AM13" s="60"/>
+      <c r="AN13" s="60"/>
+      <c r="AO13" s="60"/>
+      <c r="AP13" s="50"/>
+      <c r="AQ13" s="50"/>
+      <c r="AR13" s="50"/>
+      <c r="AS13" s="52"/>
+      <c r="AT13" s="52"/>
+      <c r="AU13" s="52"/>
+      <c r="AV13" s="52"/>
+      <c r="AW13" s="52"/>
+      <c r="AX13" s="52"/>
+      <c r="AY13" s="52"/>
+      <c r="AZ13" s="52"/>
+      <c r="BA13" s="52"/>
     </row>
     <row r="14" spans="1:53">
-      <c r="A14" s="42"/>
-      <c r="B14" s="42"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="43"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
-      <c r="J14" s="43"/>
-      <c r="K14" s="43"/>
-      <c r="L14" s="43"/>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
-      <c r="O14" s="43"/>
-      <c r="P14" s="43"/>
-      <c r="Q14" s="44"/>
-      <c r="R14" s="43"/>
-      <c r="S14" s="43"/>
-      <c r="T14" s="43"/>
-      <c r="U14" s="43"/>
-      <c r="V14" s="43"/>
-      <c r="W14" s="43"/>
-      <c r="X14" s="43"/>
-      <c r="Y14" s="43"/>
-      <c r="Z14" s="43"/>
-      <c r="AA14" s="43"/>
-      <c r="AB14" s="43"/>
-      <c r="AC14" s="43"/>
-      <c r="AD14" s="43"/>
-      <c r="AE14" s="43"/>
-      <c r="AF14" s="43"/>
-      <c r="AG14" s="43"/>
-      <c r="AH14" s="43"/>
-      <c r="AI14" s="43"/>
-      <c r="AJ14" s="43"/>
-      <c r="AK14" s="43"/>
-      <c r="AL14" s="41"/>
-      <c r="AM14" s="42"/>
-      <c r="AN14" s="42"/>
-      <c r="AO14" s="42"/>
-      <c r="AP14" s="43"/>
-      <c r="AQ14" s="43"/>
-      <c r="AR14" s="43"/>
-      <c r="AS14" s="43"/>
-      <c r="AT14" s="43"/>
-      <c r="AU14" s="43"/>
-      <c r="AV14" s="43"/>
-      <c r="AW14" s="43"/>
-      <c r="AX14" s="43"/>
-      <c r="AY14" s="43"/>
-      <c r="AZ14" s="43"/>
-      <c r="BA14" s="43"/>
+      <c r="A14" s="49"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="50"/>
+      <c r="D14" s="50"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="50"/>
+      <c r="G14" s="50"/>
+      <c r="H14" s="50"/>
+      <c r="I14" s="50"/>
+      <c r="J14" s="50"/>
+      <c r="K14" s="50"/>
+      <c r="L14" s="50"/>
+      <c r="M14" s="50"/>
+      <c r="N14" s="50"/>
+      <c r="O14" s="50"/>
+      <c r="P14" s="50"/>
+      <c r="Q14" s="51"/>
+      <c r="R14" s="50"/>
+      <c r="S14" s="50"/>
+      <c r="T14" s="50"/>
+      <c r="U14" s="50"/>
+      <c r="V14" s="50"/>
+      <c r="W14" s="50"/>
+      <c r="X14" s="50"/>
+      <c r="Y14" s="50"/>
+      <c r="Z14" s="50"/>
+      <c r="AA14" s="50"/>
+      <c r="AB14" s="50"/>
+      <c r="AC14" s="50"/>
+      <c r="AD14" s="50"/>
+      <c r="AE14" s="50"/>
+      <c r="AF14" s="50"/>
+      <c r="AG14" s="50"/>
+      <c r="AH14" s="50"/>
+      <c r="AI14" s="50"/>
+      <c r="AJ14" s="50"/>
+      <c r="AK14" s="50"/>
+      <c r="AL14" s="48"/>
+      <c r="AM14" s="49"/>
+      <c r="AN14" s="49"/>
+      <c r="AO14" s="49"/>
+      <c r="AP14" s="50"/>
+      <c r="AQ14" s="50"/>
+      <c r="AR14" s="50"/>
+      <c r="AS14" s="50"/>
+      <c r="AT14" s="50"/>
+      <c r="AU14" s="50"/>
+      <c r="AV14" s="50"/>
+      <c r="AW14" s="50"/>
+      <c r="AX14" s="50"/>
+      <c r="AY14" s="50"/>
+      <c r="AZ14" s="50"/>
+      <c r="BA14" s="50"/>
     </row>
     <row r="15" spans="1:53">
-      <c r="A15" s="42"/>
-      <c r="B15" s="42"/>
-      <c r="C15" s="43"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="43"/>
-      <c r="J15" s="43"/>
-      <c r="K15" s="43"/>
-      <c r="L15" s="43"/>
-      <c r="M15" s="43"/>
-      <c r="N15" s="43"/>
-      <c r="O15" s="43"/>
-      <c r="P15" s="43"/>
-      <c r="Q15" s="44"/>
-      <c r="R15" s="43"/>
-      <c r="S15" s="43"/>
-      <c r="T15" s="43"/>
-      <c r="U15" s="43"/>
-      <c r="V15" s="43"/>
-      <c r="W15" s="43"/>
-      <c r="X15" s="43"/>
-      <c r="Y15" s="43"/>
-      <c r="Z15" s="43"/>
-      <c r="AA15" s="43"/>
-      <c r="AB15" s="43"/>
-      <c r="AC15" s="43"/>
-      <c r="AD15" s="43"/>
-      <c r="AE15" s="43"/>
-      <c r="AF15" s="43"/>
-      <c r="AG15" s="43"/>
-      <c r="AH15" s="43"/>
-      <c r="AI15" s="43"/>
-      <c r="AJ15" s="43"/>
-      <c r="AK15" s="43"/>
-      <c r="AL15" s="41"/>
-      <c r="AM15" s="42"/>
-      <c r="AN15" s="42"/>
-      <c r="AO15" s="42"/>
-      <c r="AP15" s="43"/>
-      <c r="AQ15" s="43"/>
-      <c r="AR15" s="43"/>
-      <c r="AS15" s="43"/>
-      <c r="AT15" s="43"/>
-      <c r="AU15" s="43"/>
-      <c r="AV15" s="43"/>
-      <c r="AW15" s="43"/>
-      <c r="AX15" s="43"/>
-      <c r="AY15" s="43"/>
-      <c r="AZ15" s="43"/>
-      <c r="BA15" s="43"/>
+      <c r="A15" s="49"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="50"/>
+      <c r="D15" s="50"/>
+      <c r="E15" s="50"/>
+      <c r="F15" s="50"/>
+      <c r="G15" s="50"/>
+      <c r="H15" s="50"/>
+      <c r="I15" s="50"/>
+      <c r="J15" s="50"/>
+      <c r="K15" s="50"/>
+      <c r="L15" s="50"/>
+      <c r="M15" s="50"/>
+      <c r="N15" s="50"/>
+      <c r="O15" s="50"/>
+      <c r="P15" s="50"/>
+      <c r="Q15" s="51"/>
+      <c r="R15" s="50"/>
+      <c r="S15" s="50"/>
+      <c r="T15" s="50"/>
+      <c r="U15" s="50"/>
+      <c r="V15" s="50"/>
+      <c r="W15" s="50"/>
+      <c r="X15" s="50"/>
+      <c r="Y15" s="50"/>
+      <c r="Z15" s="50"/>
+      <c r="AA15" s="50"/>
+      <c r="AB15" s="50"/>
+      <c r="AC15" s="50"/>
+      <c r="AD15" s="50"/>
+      <c r="AE15" s="50"/>
+      <c r="AF15" s="50"/>
+      <c r="AG15" s="50"/>
+      <c r="AH15" s="50"/>
+      <c r="AI15" s="50"/>
+      <c r="AJ15" s="50"/>
+      <c r="AK15" s="50"/>
+      <c r="AL15" s="48"/>
+      <c r="AM15" s="49"/>
+      <c r="AN15" s="49"/>
+      <c r="AO15" s="49"/>
+      <c r="AP15" s="50"/>
+      <c r="AQ15" s="50"/>
+      <c r="AR15" s="50"/>
+      <c r="AS15" s="50"/>
+      <c r="AT15" s="50"/>
+      <c r="AU15" s="50"/>
+      <c r="AV15" s="50"/>
+      <c r="AW15" s="50"/>
+      <c r="AX15" s="50"/>
+      <c r="AY15" s="50"/>
+      <c r="AZ15" s="50"/>
+      <c r="BA15" s="50"/>
     </row>
     <row r="16" spans="1:53">
-      <c r="A16" s="42"/>
-      <c r="B16" s="42"/>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="43"/>
-      <c r="I16" s="43"/>
-      <c r="J16" s="43"/>
-      <c r="K16" s="43"/>
-      <c r="L16" s="43"/>
-      <c r="M16" s="43"/>
-      <c r="N16" s="43"/>
-      <c r="O16" s="43"/>
-      <c r="P16" s="43"/>
-      <c r="Q16" s="44"/>
-      <c r="R16" s="43"/>
-      <c r="S16" s="43"/>
-      <c r="T16" s="43"/>
-      <c r="U16" s="43"/>
-      <c r="V16" s="43"/>
-      <c r="W16" s="43"/>
-      <c r="X16" s="43"/>
-      <c r="Y16" s="43"/>
-      <c r="Z16" s="43"/>
-      <c r="AA16" s="43"/>
-      <c r="AB16" s="43"/>
-      <c r="AC16" s="43"/>
-      <c r="AD16" s="43"/>
-      <c r="AE16" s="43"/>
-      <c r="AF16" s="43"/>
-      <c r="AG16" s="43"/>
-      <c r="AH16" s="43"/>
-      <c r="AI16" s="43"/>
-      <c r="AJ16" s="43"/>
-      <c r="AK16" s="43"/>
-      <c r="AL16" s="41"/>
-      <c r="AM16" s="42"/>
-      <c r="AN16" s="42"/>
-      <c r="AO16" s="42"/>
-      <c r="AP16" s="43"/>
-      <c r="AQ16" s="43"/>
-      <c r="AR16" s="43"/>
-      <c r="AS16" s="43"/>
-      <c r="AT16" s="43"/>
-      <c r="AU16" s="43"/>
-      <c r="AV16" s="43"/>
-      <c r="AW16" s="43"/>
-      <c r="AX16" s="43"/>
-      <c r="AY16" s="43"/>
-      <c r="AZ16" s="43"/>
-      <c r="BA16" s="43"/>
+      <c r="A16" s="49"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="50"/>
+      <c r="D16" s="50"/>
+      <c r="E16" s="50"/>
+      <c r="F16" s="50"/>
+      <c r="G16" s="50"/>
+      <c r="H16" s="50"/>
+      <c r="I16" s="50"/>
+      <c r="J16" s="50"/>
+      <c r="K16" s="50"/>
+      <c r="L16" s="50"/>
+      <c r="M16" s="50"/>
+      <c r="N16" s="50"/>
+      <c r="O16" s="50"/>
+      <c r="P16" s="50"/>
+      <c r="Q16" s="51"/>
+      <c r="R16" s="50"/>
+      <c r="S16" s="50"/>
+      <c r="T16" s="50"/>
+      <c r="U16" s="50"/>
+      <c r="V16" s="50"/>
+      <c r="W16" s="50"/>
+      <c r="X16" s="50"/>
+      <c r="Y16" s="50"/>
+      <c r="Z16" s="50"/>
+      <c r="AA16" s="50"/>
+      <c r="AB16" s="50"/>
+      <c r="AC16" s="50"/>
+      <c r="AD16" s="50"/>
+      <c r="AE16" s="50"/>
+      <c r="AF16" s="50"/>
+      <c r="AG16" s="50"/>
+      <c r="AH16" s="50"/>
+      <c r="AI16" s="50"/>
+      <c r="AJ16" s="50"/>
+      <c r="AK16" s="50"/>
+      <c r="AL16" s="48"/>
+      <c r="AM16" s="49"/>
+      <c r="AN16" s="49"/>
+      <c r="AO16" s="49"/>
+      <c r="AP16" s="50"/>
+      <c r="AQ16" s="50"/>
+      <c r="AR16" s="50"/>
+      <c r="AS16" s="50"/>
+      <c r="AT16" s="50"/>
+      <c r="AU16" s="50"/>
+      <c r="AV16" s="50"/>
+      <c r="AW16" s="50"/>
+      <c r="AX16" s="50"/>
+      <c r="AY16" s="50"/>
+      <c r="AZ16" s="50"/>
+      <c r="BA16" s="50"/>
     </row>
     <row r="17" spans="1:53">
-      <c r="A17" s="60"/>
-      <c r="B17" s="60"/>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="43"/>
-      <c r="H17" s="43"/>
-      <c r="I17" s="43"/>
-      <c r="J17" s="43"/>
-      <c r="K17" s="43"/>
-      <c r="L17" s="43"/>
-      <c r="M17" s="43"/>
-      <c r="N17" s="43"/>
-      <c r="O17" s="43"/>
-      <c r="P17" s="43"/>
-      <c r="Q17" s="43"/>
-      <c r="R17" s="46"/>
-      <c r="S17" s="46"/>
-      <c r="T17" s="46"/>
-      <c r="U17" s="46"/>
-      <c r="V17" s="46"/>
-      <c r="W17" s="46"/>
-      <c r="X17" s="46"/>
-      <c r="Y17" s="46"/>
-      <c r="Z17" s="46"/>
-      <c r="AA17" s="46"/>
-      <c r="AB17" s="46"/>
-      <c r="AC17" s="46"/>
-      <c r="AD17" s="46"/>
-      <c r="AE17" s="46"/>
-      <c r="AF17" s="46"/>
-      <c r="AG17" s="46"/>
-      <c r="AH17" s="46"/>
-      <c r="AI17" s="46"/>
-      <c r="AJ17" s="46"/>
-      <c r="AK17" s="46"/>
-      <c r="AL17" s="41"/>
-      <c r="AM17" s="42"/>
-      <c r="AN17" s="42"/>
-      <c r="AO17" s="42"/>
-      <c r="AP17" s="43"/>
-      <c r="AQ17" s="46"/>
-      <c r="AR17" s="46"/>
-      <c r="AS17" s="46"/>
-      <c r="AT17" s="46"/>
-      <c r="AU17" s="46"/>
-      <c r="AV17" s="46"/>
-      <c r="AW17" s="46"/>
-      <c r="AX17" s="46"/>
-      <c r="AY17" s="46"/>
-      <c r="AZ17" s="46"/>
-      <c r="BA17" s="46"/>
+      <c r="A17" s="67"/>
+      <c r="B17" s="67"/>
+      <c r="C17" s="50"/>
+      <c r="D17" s="50"/>
+      <c r="E17" s="50"/>
+      <c r="F17" s="50"/>
+      <c r="G17" s="50"/>
+      <c r="H17" s="50"/>
+      <c r="I17" s="50"/>
+      <c r="J17" s="50"/>
+      <c r="K17" s="50"/>
+      <c r="L17" s="50"/>
+      <c r="M17" s="50"/>
+      <c r="N17" s="50"/>
+      <c r="O17" s="50"/>
+      <c r="P17" s="50"/>
+      <c r="Q17" s="50"/>
+      <c r="R17" s="53"/>
+      <c r="S17" s="53"/>
+      <c r="T17" s="53"/>
+      <c r="U17" s="53"/>
+      <c r="V17" s="53"/>
+      <c r="W17" s="53"/>
+      <c r="X17" s="53"/>
+      <c r="Y17" s="53"/>
+      <c r="Z17" s="53"/>
+      <c r="AA17" s="53"/>
+      <c r="AB17" s="53"/>
+      <c r="AC17" s="53"/>
+      <c r="AD17" s="53"/>
+      <c r="AE17" s="53"/>
+      <c r="AF17" s="53"/>
+      <c r="AG17" s="53"/>
+      <c r="AH17" s="53"/>
+      <c r="AI17" s="53"/>
+      <c r="AJ17" s="53"/>
+      <c r="AK17" s="53"/>
+      <c r="AL17" s="48"/>
+      <c r="AM17" s="49"/>
+      <c r="AN17" s="49"/>
+      <c r="AO17" s="49"/>
+      <c r="AP17" s="50"/>
+      <c r="AQ17" s="53"/>
+      <c r="AR17" s="53"/>
+      <c r="AS17" s="53"/>
+      <c r="AT17" s="53"/>
+      <c r="AU17" s="53"/>
+      <c r="AV17" s="53"/>
+      <c r="AW17" s="53"/>
+      <c r="AX17" s="53"/>
+      <c r="AY17" s="53"/>
+      <c r="AZ17" s="53"/>
+      <c r="BA17" s="53"/>
     </row>
     <row r="18" spans="1:53">
-      <c r="A18" s="60"/>
-      <c r="B18" s="60"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="43"/>
-      <c r="K18" s="43"/>
-      <c r="L18" s="43"/>
-      <c r="M18" s="43"/>
-      <c r="N18" s="43"/>
-      <c r="O18" s="43"/>
-      <c r="P18" s="43"/>
-      <c r="Q18" s="43"/>
-      <c r="R18" s="46"/>
-      <c r="S18" s="46"/>
-      <c r="T18" s="46"/>
-      <c r="U18" s="46"/>
-      <c r="V18" s="46"/>
-      <c r="W18" s="46"/>
-      <c r="X18" s="46"/>
-      <c r="Y18" s="46"/>
-      <c r="Z18" s="46"/>
-      <c r="AA18" s="46"/>
-      <c r="AB18" s="46"/>
-      <c r="AC18" s="46"/>
-      <c r="AD18" s="46"/>
-      <c r="AE18" s="46"/>
-      <c r="AF18" s="46"/>
-      <c r="AG18" s="46"/>
-      <c r="AH18" s="46"/>
-      <c r="AI18" s="46"/>
-      <c r="AJ18" s="46"/>
-      <c r="AK18" s="46"/>
-      <c r="AL18" s="41"/>
-      <c r="AM18" s="42"/>
-      <c r="AN18" s="42"/>
-      <c r="AO18" s="42"/>
-      <c r="AP18" s="43"/>
-      <c r="AQ18" s="46"/>
-      <c r="AR18" s="46"/>
-      <c r="AS18" s="46"/>
-      <c r="AT18" s="46"/>
-      <c r="AU18" s="46"/>
-      <c r="AV18" s="46"/>
-      <c r="AW18" s="46"/>
-      <c r="AX18" s="46"/>
-      <c r="AY18" s="46"/>
-      <c r="AZ18" s="46"/>
-      <c r="BA18" s="46"/>
+      <c r="A18" s="67"/>
+      <c r="B18" s="67"/>
+      <c r="C18" s="50"/>
+      <c r="D18" s="50"/>
+      <c r="E18" s="50"/>
+      <c r="F18" s="50"/>
+      <c r="G18" s="50"/>
+      <c r="H18" s="50"/>
+      <c r="I18" s="50"/>
+      <c r="J18" s="50"/>
+      <c r="K18" s="50"/>
+      <c r="L18" s="50"/>
+      <c r="M18" s="50"/>
+      <c r="N18" s="50"/>
+      <c r="O18" s="50"/>
+      <c r="P18" s="50"/>
+      <c r="Q18" s="50"/>
+      <c r="R18" s="53"/>
+      <c r="S18" s="53"/>
+      <c r="T18" s="53"/>
+      <c r="U18" s="53"/>
+      <c r="V18" s="53"/>
+      <c r="W18" s="53"/>
+      <c r="X18" s="53"/>
+      <c r="Y18" s="53"/>
+      <c r="Z18" s="53"/>
+      <c r="AA18" s="53"/>
+      <c r="AB18" s="53"/>
+      <c r="AC18" s="53"/>
+      <c r="AD18" s="53"/>
+      <c r="AE18" s="53"/>
+      <c r="AF18" s="53"/>
+      <c r="AG18" s="53"/>
+      <c r="AH18" s="53"/>
+      <c r="AI18" s="53"/>
+      <c r="AJ18" s="53"/>
+      <c r="AK18" s="53"/>
+      <c r="AL18" s="48"/>
+      <c r="AM18" s="49"/>
+      <c r="AN18" s="49"/>
+      <c r="AO18" s="49"/>
+      <c r="AP18" s="50"/>
+      <c r="AQ18" s="53"/>
+      <c r="AR18" s="53"/>
+      <c r="AS18" s="53"/>
+      <c r="AT18" s="53"/>
+      <c r="AU18" s="53"/>
+      <c r="AV18" s="53"/>
+      <c r="AW18" s="53"/>
+      <c r="AX18" s="53"/>
+      <c r="AY18" s="53"/>
+      <c r="AZ18" s="53"/>
+      <c r="BA18" s="53"/>
     </row>
     <row r="19" spans="1:53">
-      <c r="A19" s="42"/>
-      <c r="B19" s="42"/>
-      <c r="C19" s="43"/>
-      <c r="D19" s="43"/>
-      <c r="E19" s="43"/>
-      <c r="F19" s="43"/>
-      <c r="G19" s="43"/>
-      <c r="H19" s="43"/>
-      <c r="I19" s="43"/>
-      <c r="J19" s="43"/>
-      <c r="K19" s="43"/>
-      <c r="L19" s="43"/>
-      <c r="M19" s="43"/>
-      <c r="N19" s="43"/>
-      <c r="O19" s="43"/>
-      <c r="P19" s="43"/>
-      <c r="Q19" s="43"/>
-      <c r="R19" s="43"/>
-      <c r="S19" s="43"/>
-      <c r="T19" s="43"/>
-      <c r="U19" s="43"/>
-      <c r="V19" s="43"/>
-      <c r="W19" s="43"/>
-      <c r="X19" s="43"/>
-      <c r="Y19" s="43"/>
-      <c r="Z19" s="43"/>
-      <c r="AA19" s="43"/>
-      <c r="AB19" s="43"/>
-      <c r="AC19" s="43"/>
-      <c r="AD19" s="43"/>
-      <c r="AE19" s="43"/>
-      <c r="AF19" s="43"/>
-      <c r="AG19" s="43"/>
-      <c r="AH19" s="43"/>
-      <c r="AI19" s="43"/>
-      <c r="AJ19" s="43"/>
-      <c r="AK19" s="43"/>
-      <c r="AL19" s="41"/>
-      <c r="AM19" s="41"/>
-      <c r="AN19" s="41"/>
-      <c r="AO19" s="41"/>
-      <c r="AP19" s="43"/>
-      <c r="AQ19" s="43"/>
-      <c r="AR19" s="43"/>
-      <c r="AS19" s="43"/>
-      <c r="AT19" s="43"/>
-      <c r="AU19" s="43"/>
-      <c r="AV19" s="43"/>
-      <c r="AW19" s="43"/>
-      <c r="AX19" s="43"/>
-      <c r="AY19" s="43"/>
-      <c r="AZ19" s="43"/>
-      <c r="BA19" s="43"/>
+      <c r="A19" s="49"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="50"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="50"/>
+      <c r="F19" s="50"/>
+      <c r="G19" s="50"/>
+      <c r="H19" s="50"/>
+      <c r="I19" s="50"/>
+      <c r="J19" s="50"/>
+      <c r="K19" s="50"/>
+      <c r="L19" s="50"/>
+      <c r="M19" s="50"/>
+      <c r="N19" s="50"/>
+      <c r="O19" s="50"/>
+      <c r="P19" s="50"/>
+      <c r="Q19" s="50"/>
+      <c r="R19" s="50"/>
+      <c r="S19" s="50"/>
+      <c r="T19" s="50"/>
+      <c r="U19" s="50"/>
+      <c r="V19" s="50"/>
+      <c r="W19" s="50"/>
+      <c r="X19" s="50"/>
+      <c r="Y19" s="50"/>
+      <c r="Z19" s="50"/>
+      <c r="AA19" s="50"/>
+      <c r="AB19" s="50"/>
+      <c r="AC19" s="50"/>
+      <c r="AD19" s="50"/>
+      <c r="AE19" s="50"/>
+      <c r="AF19" s="50"/>
+      <c r="AG19" s="50"/>
+      <c r="AH19" s="50"/>
+      <c r="AI19" s="50"/>
+      <c r="AJ19" s="50"/>
+      <c r="AK19" s="50"/>
+      <c r="AL19" s="48"/>
+      <c r="AM19" s="48"/>
+      <c r="AN19" s="48"/>
+      <c r="AO19" s="48"/>
+      <c r="AP19" s="50"/>
+      <c r="AQ19" s="50"/>
+      <c r="AR19" s="50"/>
+      <c r="AS19" s="50"/>
+      <c r="AT19" s="50"/>
+      <c r="AU19" s="50"/>
+      <c r="AV19" s="50"/>
+      <c r="AW19" s="50"/>
+      <c r="AX19" s="50"/>
+      <c r="AY19" s="50"/>
+      <c r="AZ19" s="50"/>
+      <c r="BA19" s="50"/>
     </row>
     <row r="20" spans="1:53">
-      <c r="A20" s="42"/>
-      <c r="B20" s="42"/>
-      <c r="C20" s="43"/>
-      <c r="D20" s="43"/>
-      <c r="E20" s="43"/>
-      <c r="F20" s="43"/>
-      <c r="G20" s="43"/>
-      <c r="H20" s="43"/>
-      <c r="I20" s="43"/>
-      <c r="J20" s="43"/>
-      <c r="K20" s="43"/>
-      <c r="L20" s="43"/>
-      <c r="M20" s="43"/>
-      <c r="N20" s="43"/>
-      <c r="O20" s="43"/>
-      <c r="P20" s="43"/>
-      <c r="Q20" s="43"/>
-      <c r="R20" s="43"/>
-      <c r="S20" s="43"/>
-      <c r="T20" s="43"/>
-      <c r="U20" s="43"/>
-      <c r="V20" s="43"/>
-      <c r="W20" s="43"/>
-      <c r="X20" s="43"/>
-      <c r="Y20" s="43"/>
-      <c r="Z20" s="43"/>
-      <c r="AA20" s="43"/>
-      <c r="AB20" s="43"/>
-      <c r="AC20" s="43"/>
-      <c r="AD20" s="43"/>
-      <c r="AE20" s="43"/>
-      <c r="AF20" s="43"/>
-      <c r="AG20" s="43"/>
-      <c r="AH20" s="43"/>
-      <c r="AI20" s="43"/>
-      <c r="AJ20" s="43"/>
-      <c r="AK20" s="43"/>
-      <c r="AL20" s="41"/>
-      <c r="AM20" s="41"/>
-      <c r="AN20" s="41"/>
-      <c r="AO20" s="41"/>
-      <c r="AP20" s="43"/>
-      <c r="AQ20" s="43"/>
-      <c r="AR20" s="43"/>
-      <c r="AS20" s="43"/>
-      <c r="AT20" s="43"/>
-      <c r="AU20" s="43"/>
-      <c r="AV20" s="43"/>
-      <c r="AW20" s="43"/>
-      <c r="AX20" s="43"/>
-      <c r="AY20" s="43"/>
-      <c r="AZ20" s="43"/>
-      <c r="BA20" s="43"/>
+      <c r="A20" s="49"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="50"/>
+      <c r="D20" s="50"/>
+      <c r="E20" s="50"/>
+      <c r="F20" s="50"/>
+      <c r="G20" s="50"/>
+      <c r="H20" s="50"/>
+      <c r="I20" s="50"/>
+      <c r="J20" s="50"/>
+      <c r="K20" s="50"/>
+      <c r="L20" s="50"/>
+      <c r="M20" s="50"/>
+      <c r="N20" s="50"/>
+      <c r="O20" s="50"/>
+      <c r="P20" s="50"/>
+      <c r="Q20" s="50"/>
+      <c r="R20" s="50"/>
+      <c r="S20" s="50"/>
+      <c r="T20" s="50"/>
+      <c r="U20" s="50"/>
+      <c r="V20" s="50"/>
+      <c r="W20" s="50"/>
+      <c r="X20" s="50"/>
+      <c r="Y20" s="50"/>
+      <c r="Z20" s="50"/>
+      <c r="AA20" s="50"/>
+      <c r="AB20" s="50"/>
+      <c r="AC20" s="50"/>
+      <c r="AD20" s="50"/>
+      <c r="AE20" s="50"/>
+      <c r="AF20" s="50"/>
+      <c r="AG20" s="50"/>
+      <c r="AH20" s="50"/>
+      <c r="AI20" s="50"/>
+      <c r="AJ20" s="50"/>
+      <c r="AK20" s="50"/>
+      <c r="AL20" s="48"/>
+      <c r="AM20" s="48"/>
+      <c r="AN20" s="48"/>
+      <c r="AO20" s="48"/>
+      <c r="AP20" s="50"/>
+      <c r="AQ20" s="50"/>
+      <c r="AR20" s="50"/>
+      <c r="AS20" s="50"/>
+      <c r="AT20" s="50"/>
+      <c r="AU20" s="50"/>
+      <c r="AV20" s="50"/>
+      <c r="AW20" s="50"/>
+      <c r="AX20" s="50"/>
+      <c r="AY20" s="50"/>
+      <c r="AZ20" s="50"/>
+      <c r="BA20" s="50"/>
     </row>
     <row r="21" spans="1:53" ht="13.5" customHeight="1">
-      <c r="A21" s="42"/>
-      <c r="B21" s="42"/>
-      <c r="C21" s="43"/>
-      <c r="D21" s="43"/>
-      <c r="E21" s="43"/>
-      <c r="F21" s="43"/>
-      <c r="G21" s="43"/>
-      <c r="H21" s="43"/>
-      <c r="I21" s="43"/>
-      <c r="J21" s="43"/>
-      <c r="K21" s="43"/>
-      <c r="L21" s="43"/>
-      <c r="M21" s="43"/>
-      <c r="N21" s="43"/>
-      <c r="O21" s="43"/>
-      <c r="P21" s="43"/>
-      <c r="Q21" s="43"/>
-      <c r="R21" s="46"/>
-      <c r="S21" s="46"/>
-      <c r="T21" s="46"/>
-      <c r="U21" s="46"/>
-      <c r="V21" s="46"/>
-      <c r="W21" s="46"/>
-      <c r="X21" s="46"/>
-      <c r="Y21" s="46"/>
-      <c r="Z21" s="46"/>
-      <c r="AA21" s="46"/>
-      <c r="AB21" s="46"/>
-      <c r="AC21" s="46"/>
-      <c r="AD21" s="46"/>
-      <c r="AE21" s="46"/>
-      <c r="AF21" s="46"/>
-      <c r="AG21" s="46"/>
-      <c r="AH21" s="46"/>
-      <c r="AI21" s="46"/>
-      <c r="AJ21" s="46"/>
-      <c r="AK21" s="46"/>
-      <c r="AL21" s="41"/>
-      <c r="AM21" s="41"/>
-      <c r="AN21" s="41"/>
-      <c r="AO21" s="41"/>
-      <c r="AP21" s="43"/>
-      <c r="AQ21" s="43"/>
-      <c r="AR21" s="43"/>
-      <c r="AS21" s="43"/>
-      <c r="AT21" s="43"/>
-      <c r="AU21" s="43"/>
-      <c r="AV21" s="43"/>
-      <c r="AW21" s="43"/>
-      <c r="AX21" s="43"/>
-      <c r="AY21" s="43"/>
-      <c r="AZ21" s="43"/>
-      <c r="BA21" s="43"/>
+      <c r="A21" s="49"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="50"/>
+      <c r="D21" s="50"/>
+      <c r="E21" s="50"/>
+      <c r="F21" s="50"/>
+      <c r="G21" s="50"/>
+      <c r="H21" s="50"/>
+      <c r="I21" s="50"/>
+      <c r="J21" s="50"/>
+      <c r="K21" s="50"/>
+      <c r="L21" s="50"/>
+      <c r="M21" s="50"/>
+      <c r="N21" s="50"/>
+      <c r="O21" s="50"/>
+      <c r="P21" s="50"/>
+      <c r="Q21" s="50"/>
+      <c r="R21" s="53"/>
+      <c r="S21" s="53"/>
+      <c r="T21" s="53"/>
+      <c r="U21" s="53"/>
+      <c r="V21" s="53"/>
+      <c r="W21" s="53"/>
+      <c r="X21" s="53"/>
+      <c r="Y21" s="53"/>
+      <c r="Z21" s="53"/>
+      <c r="AA21" s="53"/>
+      <c r="AB21" s="53"/>
+      <c r="AC21" s="53"/>
+      <c r="AD21" s="53"/>
+      <c r="AE21" s="53"/>
+      <c r="AF21" s="53"/>
+      <c r="AG21" s="53"/>
+      <c r="AH21" s="53"/>
+      <c r="AI21" s="53"/>
+      <c r="AJ21" s="53"/>
+      <c r="AK21" s="53"/>
+      <c r="AL21" s="48"/>
+      <c r="AM21" s="48"/>
+      <c r="AN21" s="48"/>
+      <c r="AO21" s="48"/>
+      <c r="AP21" s="50"/>
+      <c r="AQ21" s="50"/>
+      <c r="AR21" s="50"/>
+      <c r="AS21" s="50"/>
+      <c r="AT21" s="50"/>
+      <c r="AU21" s="50"/>
+      <c r="AV21" s="50"/>
+      <c r="AW21" s="50"/>
+      <c r="AX21" s="50"/>
+      <c r="AY21" s="50"/>
+      <c r="AZ21" s="50"/>
+      <c r="BA21" s="50"/>
     </row>
     <row r="22" spans="1:53">
-      <c r="A22" s="42"/>
-      <c r="B22" s="42"/>
-      <c r="C22" s="43"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="43"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="43"/>
-      <c r="I22" s="43"/>
-      <c r="J22" s="43"/>
-      <c r="K22" s="43"/>
-      <c r="L22" s="43"/>
-      <c r="M22" s="43"/>
-      <c r="N22" s="43"/>
-      <c r="O22" s="43"/>
-      <c r="P22" s="43"/>
-      <c r="Q22" s="43"/>
-      <c r="R22" s="43"/>
-      <c r="S22" s="43"/>
-      <c r="T22" s="43"/>
-      <c r="U22" s="43"/>
-      <c r="V22" s="43"/>
-      <c r="W22" s="43"/>
-      <c r="X22" s="43"/>
-      <c r="Y22" s="43"/>
-      <c r="Z22" s="43"/>
-      <c r="AA22" s="43"/>
-      <c r="AB22" s="43"/>
-      <c r="AC22" s="43"/>
-      <c r="AD22" s="43"/>
-      <c r="AE22" s="43"/>
-      <c r="AF22" s="43"/>
-      <c r="AG22" s="43"/>
-      <c r="AH22" s="43"/>
-      <c r="AI22" s="43"/>
-      <c r="AJ22" s="43"/>
-      <c r="AK22" s="43"/>
-      <c r="AL22" s="41"/>
-      <c r="AM22" s="41"/>
-      <c r="AN22" s="41"/>
-      <c r="AO22" s="41"/>
-      <c r="AP22" s="43"/>
-      <c r="AQ22" s="43"/>
-      <c r="AR22" s="43"/>
-      <c r="AS22" s="43"/>
-      <c r="AT22" s="43"/>
-      <c r="AU22" s="43"/>
-      <c r="AV22" s="43"/>
-      <c r="AW22" s="43"/>
-      <c r="AX22" s="43"/>
-      <c r="AY22" s="43"/>
-      <c r="AZ22" s="43"/>
-      <c r="BA22" s="43"/>
+      <c r="A22" s="49"/>
+      <c r="B22" s="49"/>
+      <c r="C22" s="50"/>
+      <c r="D22" s="50"/>
+      <c r="E22" s="50"/>
+      <c r="F22" s="50"/>
+      <c r="G22" s="50"/>
+      <c r="H22" s="50"/>
+      <c r="I22" s="50"/>
+      <c r="J22" s="50"/>
+      <c r="K22" s="50"/>
+      <c r="L22" s="50"/>
+      <c r="M22" s="50"/>
+      <c r="N22" s="50"/>
+      <c r="O22" s="50"/>
+      <c r="P22" s="50"/>
+      <c r="Q22" s="50"/>
+      <c r="R22" s="50"/>
+      <c r="S22" s="50"/>
+      <c r="T22" s="50"/>
+      <c r="U22" s="50"/>
+      <c r="V22" s="50"/>
+      <c r="W22" s="50"/>
+      <c r="X22" s="50"/>
+      <c r="Y22" s="50"/>
+      <c r="Z22" s="50"/>
+      <c r="AA22" s="50"/>
+      <c r="AB22" s="50"/>
+      <c r="AC22" s="50"/>
+      <c r="AD22" s="50"/>
+      <c r="AE22" s="50"/>
+      <c r="AF22" s="50"/>
+      <c r="AG22" s="50"/>
+      <c r="AH22" s="50"/>
+      <c r="AI22" s="50"/>
+      <c r="AJ22" s="50"/>
+      <c r="AK22" s="50"/>
+      <c r="AL22" s="48"/>
+      <c r="AM22" s="48"/>
+      <c r="AN22" s="48"/>
+      <c r="AO22" s="48"/>
+      <c r="AP22" s="50"/>
+      <c r="AQ22" s="50"/>
+      <c r="AR22" s="50"/>
+      <c r="AS22" s="50"/>
+      <c r="AT22" s="50"/>
+      <c r="AU22" s="50"/>
+      <c r="AV22" s="50"/>
+      <c r="AW22" s="50"/>
+      <c r="AX22" s="50"/>
+      <c r="AY22" s="50"/>
+      <c r="AZ22" s="50"/>
+      <c r="BA22" s="50"/>
     </row>
     <row r="23" spans="1:53">
-      <c r="A23" s="42"/>
-      <c r="B23" s="42"/>
-      <c r="C23" s="43"/>
-      <c r="D23" s="43"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="43"/>
-      <c r="G23" s="43"/>
-      <c r="H23" s="43"/>
-      <c r="I23" s="43"/>
-      <c r="J23" s="43"/>
-      <c r="K23" s="43"/>
-      <c r="L23" s="43"/>
-      <c r="M23" s="43"/>
-      <c r="N23" s="43"/>
-      <c r="O23" s="43"/>
-      <c r="P23" s="43"/>
-      <c r="Q23" s="43"/>
-      <c r="R23" s="46"/>
-      <c r="S23" s="46"/>
-      <c r="T23" s="46"/>
-      <c r="U23" s="46"/>
-      <c r="V23" s="46"/>
-      <c r="W23" s="46"/>
-      <c r="X23" s="46"/>
-      <c r="Y23" s="46"/>
-      <c r="Z23" s="46"/>
-      <c r="AA23" s="46"/>
-      <c r="AB23" s="46"/>
-      <c r="AC23" s="46"/>
-      <c r="AD23" s="46"/>
-      <c r="AE23" s="46"/>
-      <c r="AF23" s="46"/>
-      <c r="AG23" s="46"/>
-      <c r="AH23" s="46"/>
-      <c r="AI23" s="46"/>
-      <c r="AJ23" s="46"/>
-      <c r="AK23" s="46"/>
-      <c r="AL23" s="41"/>
-      <c r="AM23" s="41"/>
-      <c r="AN23" s="41"/>
-      <c r="AO23" s="41"/>
-      <c r="AP23" s="43"/>
-      <c r="AQ23" s="43"/>
-      <c r="AR23" s="43"/>
-      <c r="AS23" s="43"/>
-      <c r="AT23" s="43"/>
-      <c r="AU23" s="43"/>
-      <c r="AV23" s="43"/>
-      <c r="AW23" s="43"/>
-      <c r="AX23" s="43"/>
-      <c r="AY23" s="43"/>
-      <c r="AZ23" s="43"/>
-      <c r="BA23" s="43"/>
+      <c r="A23" s="49"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="50"/>
+      <c r="D23" s="50"/>
+      <c r="E23" s="50"/>
+      <c r="F23" s="50"/>
+      <c r="G23" s="50"/>
+      <c r="H23" s="50"/>
+      <c r="I23" s="50"/>
+      <c r="J23" s="50"/>
+      <c r="K23" s="50"/>
+      <c r="L23" s="50"/>
+      <c r="M23" s="50"/>
+      <c r="N23" s="50"/>
+      <c r="O23" s="50"/>
+      <c r="P23" s="50"/>
+      <c r="Q23" s="50"/>
+      <c r="R23" s="53"/>
+      <c r="S23" s="53"/>
+      <c r="T23" s="53"/>
+      <c r="U23" s="53"/>
+      <c r="V23" s="53"/>
+      <c r="W23" s="53"/>
+      <c r="X23" s="53"/>
+      <c r="Y23" s="53"/>
+      <c r="Z23" s="53"/>
+      <c r="AA23" s="53"/>
+      <c r="AB23" s="53"/>
+      <c r="AC23" s="53"/>
+      <c r="AD23" s="53"/>
+      <c r="AE23" s="53"/>
+      <c r="AF23" s="53"/>
+      <c r="AG23" s="53"/>
+      <c r="AH23" s="53"/>
+      <c r="AI23" s="53"/>
+      <c r="AJ23" s="53"/>
+      <c r="AK23" s="53"/>
+      <c r="AL23" s="48"/>
+      <c r="AM23" s="48"/>
+      <c r="AN23" s="48"/>
+      <c r="AO23" s="48"/>
+      <c r="AP23" s="50"/>
+      <c r="AQ23" s="50"/>
+      <c r="AR23" s="50"/>
+      <c r="AS23" s="50"/>
+      <c r="AT23" s="50"/>
+      <c r="AU23" s="50"/>
+      <c r="AV23" s="50"/>
+      <c r="AW23" s="50"/>
+      <c r="AX23" s="50"/>
+      <c r="AY23" s="50"/>
+      <c r="AZ23" s="50"/>
+      <c r="BA23" s="50"/>
     </row>
     <row r="24" spans="1:53">
-      <c r="A24" s="42"/>
-      <c r="B24" s="42"/>
-      <c r="C24" s="43"/>
-      <c r="D24" s="43"/>
-      <c r="E24" s="43"/>
-      <c r="F24" s="43"/>
-      <c r="G24" s="43"/>
-      <c r="H24" s="43"/>
-      <c r="I24" s="43"/>
-      <c r="J24" s="43"/>
-      <c r="K24" s="43"/>
-      <c r="L24" s="43"/>
-      <c r="M24" s="43"/>
-      <c r="N24" s="43"/>
-      <c r="O24" s="43"/>
-      <c r="P24" s="43"/>
-      <c r="Q24" s="43"/>
-      <c r="R24" s="43"/>
-      <c r="S24" s="43"/>
-      <c r="T24" s="43"/>
-      <c r="U24" s="43"/>
-      <c r="V24" s="43"/>
-      <c r="W24" s="43"/>
-      <c r="X24" s="43"/>
-      <c r="Y24" s="43"/>
-      <c r="Z24" s="43"/>
-      <c r="AA24" s="43"/>
-      <c r="AB24" s="43"/>
-      <c r="AC24" s="43"/>
-      <c r="AD24" s="43"/>
-      <c r="AE24" s="43"/>
-      <c r="AF24" s="43"/>
-      <c r="AG24" s="43"/>
-      <c r="AH24" s="43"/>
-      <c r="AI24" s="43"/>
-      <c r="AJ24" s="43"/>
-      <c r="AK24" s="43"/>
-      <c r="AL24" s="41"/>
-      <c r="AM24" s="41"/>
-      <c r="AN24" s="41"/>
-      <c r="AO24" s="41"/>
-      <c r="AP24" s="43"/>
-      <c r="AQ24" s="43"/>
-      <c r="AR24" s="43"/>
-      <c r="AS24" s="43"/>
-      <c r="AT24" s="43"/>
-      <c r="AU24" s="43"/>
-      <c r="AV24" s="43"/>
-      <c r="AW24" s="43"/>
-      <c r="AX24" s="43"/>
-      <c r="AY24" s="43"/>
-      <c r="AZ24" s="43"/>
-      <c r="BA24" s="43"/>
+      <c r="A24" s="49"/>
+      <c r="B24" s="49"/>
+      <c r="C24" s="50"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="50"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="50"/>
+      <c r="H24" s="50"/>
+      <c r="I24" s="50"/>
+      <c r="J24" s="50"/>
+      <c r="K24" s="50"/>
+      <c r="L24" s="50"/>
+      <c r="M24" s="50"/>
+      <c r="N24" s="50"/>
+      <c r="O24" s="50"/>
+      <c r="P24" s="50"/>
+      <c r="Q24" s="50"/>
+      <c r="R24" s="50"/>
+      <c r="S24" s="50"/>
+      <c r="T24" s="50"/>
+      <c r="U24" s="50"/>
+      <c r="V24" s="50"/>
+      <c r="W24" s="50"/>
+      <c r="X24" s="50"/>
+      <c r="Y24" s="50"/>
+      <c r="Z24" s="50"/>
+      <c r="AA24" s="50"/>
+      <c r="AB24" s="50"/>
+      <c r="AC24" s="50"/>
+      <c r="AD24" s="50"/>
+      <c r="AE24" s="50"/>
+      <c r="AF24" s="50"/>
+      <c r="AG24" s="50"/>
+      <c r="AH24" s="50"/>
+      <c r="AI24" s="50"/>
+      <c r="AJ24" s="50"/>
+      <c r="AK24" s="50"/>
+      <c r="AL24" s="48"/>
+      <c r="AM24" s="48"/>
+      <c r="AN24" s="48"/>
+      <c r="AO24" s="48"/>
+      <c r="AP24" s="50"/>
+      <c r="AQ24" s="50"/>
+      <c r="AR24" s="50"/>
+      <c r="AS24" s="50"/>
+      <c r="AT24" s="50"/>
+      <c r="AU24" s="50"/>
+      <c r="AV24" s="50"/>
+      <c r="AW24" s="50"/>
+      <c r="AX24" s="50"/>
+      <c r="AY24" s="50"/>
+      <c r="AZ24" s="50"/>
+      <c r="BA24" s="50"/>
     </row>
     <row r="25" spans="1:53">
-      <c r="A25" s="42"/>
-      <c r="B25" s="42"/>
-      <c r="C25" s="43"/>
-      <c r="D25" s="43"/>
-      <c r="E25" s="43"/>
-      <c r="F25" s="43"/>
-      <c r="G25" s="43"/>
-      <c r="H25" s="43"/>
-      <c r="I25" s="43"/>
-      <c r="J25" s="43"/>
-      <c r="K25" s="43"/>
-      <c r="L25" s="43"/>
-      <c r="M25" s="43"/>
-      <c r="N25" s="43"/>
-      <c r="O25" s="43"/>
-      <c r="P25" s="43"/>
-      <c r="Q25" s="43"/>
-      <c r="R25" s="43"/>
-      <c r="S25" s="43"/>
-      <c r="T25" s="43"/>
-      <c r="U25" s="43"/>
-      <c r="V25" s="43"/>
-      <c r="W25" s="43"/>
-      <c r="X25" s="43"/>
-      <c r="Y25" s="43"/>
-      <c r="Z25" s="43"/>
-      <c r="AA25" s="43"/>
-      <c r="AB25" s="43"/>
-      <c r="AC25" s="43"/>
-      <c r="AD25" s="43"/>
-      <c r="AE25" s="43"/>
-      <c r="AF25" s="43"/>
-      <c r="AG25" s="43"/>
-      <c r="AH25" s="43"/>
-      <c r="AI25" s="43"/>
-      <c r="AJ25" s="43"/>
-      <c r="AK25" s="43"/>
-      <c r="AL25" s="41"/>
-      <c r="AM25" s="42"/>
-      <c r="AN25" s="42"/>
-      <c r="AO25" s="42"/>
-      <c r="AP25" s="43"/>
-      <c r="AQ25" s="43"/>
-      <c r="AR25" s="43"/>
-      <c r="AS25" s="43"/>
-      <c r="AT25" s="43"/>
-      <c r="AU25" s="43"/>
-      <c r="AV25" s="43"/>
-      <c r="AW25" s="43"/>
-      <c r="AX25" s="43"/>
-      <c r="AY25" s="43"/>
-      <c r="AZ25" s="43"/>
-      <c r="BA25" s="43"/>
+      <c r="A25" s="49"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="50"/>
+      <c r="D25" s="50"/>
+      <c r="E25" s="50"/>
+      <c r="F25" s="50"/>
+      <c r="G25" s="50"/>
+      <c r="H25" s="50"/>
+      <c r="I25" s="50"/>
+      <c r="J25" s="50"/>
+      <c r="K25" s="50"/>
+      <c r="L25" s="50"/>
+      <c r="M25" s="50"/>
+      <c r="N25" s="50"/>
+      <c r="O25" s="50"/>
+      <c r="P25" s="50"/>
+      <c r="Q25" s="50"/>
+      <c r="R25" s="50"/>
+      <c r="S25" s="50"/>
+      <c r="T25" s="50"/>
+      <c r="U25" s="50"/>
+      <c r="V25" s="50"/>
+      <c r="W25" s="50"/>
+      <c r="X25" s="50"/>
+      <c r="Y25" s="50"/>
+      <c r="Z25" s="50"/>
+      <c r="AA25" s="50"/>
+      <c r="AB25" s="50"/>
+      <c r="AC25" s="50"/>
+      <c r="AD25" s="50"/>
+      <c r="AE25" s="50"/>
+      <c r="AF25" s="50"/>
+      <c r="AG25" s="50"/>
+      <c r="AH25" s="50"/>
+      <c r="AI25" s="50"/>
+      <c r="AJ25" s="50"/>
+      <c r="AK25" s="50"/>
+      <c r="AL25" s="48"/>
+      <c r="AM25" s="49"/>
+      <c r="AN25" s="49"/>
+      <c r="AO25" s="49"/>
+      <c r="AP25" s="50"/>
+      <c r="AQ25" s="50"/>
+      <c r="AR25" s="50"/>
+      <c r="AS25" s="50"/>
+      <c r="AT25" s="50"/>
+      <c r="AU25" s="50"/>
+      <c r="AV25" s="50"/>
+      <c r="AW25" s="50"/>
+      <c r="AX25" s="50"/>
+      <c r="AY25" s="50"/>
+      <c r="AZ25" s="50"/>
+      <c r="BA25" s="50"/>
     </row>
     <row r="26" spans="1:53">
-      <c r="A26" s="42"/>
-      <c r="B26" s="42"/>
-      <c r="C26" s="43"/>
-      <c r="D26" s="43"/>
-      <c r="E26" s="43"/>
-      <c r="F26" s="43"/>
-      <c r="G26" s="43"/>
-      <c r="H26" s="43"/>
-      <c r="I26" s="43"/>
-      <c r="J26" s="43"/>
-      <c r="K26" s="43"/>
-      <c r="L26" s="43"/>
-      <c r="M26" s="43"/>
-      <c r="N26" s="43"/>
-      <c r="O26" s="43"/>
-      <c r="P26" s="43"/>
-      <c r="Q26" s="43"/>
-      <c r="R26" s="43"/>
-      <c r="S26" s="43"/>
-      <c r="T26" s="43"/>
-      <c r="U26" s="43"/>
-      <c r="V26" s="43"/>
-      <c r="W26" s="43"/>
-      <c r="X26" s="43"/>
-      <c r="Y26" s="43"/>
-      <c r="Z26" s="43"/>
-      <c r="AA26" s="43"/>
-      <c r="AB26" s="43"/>
-      <c r="AC26" s="43"/>
-      <c r="AD26" s="43"/>
-      <c r="AE26" s="43"/>
-      <c r="AF26" s="43"/>
-      <c r="AG26" s="43"/>
-      <c r="AH26" s="43"/>
-      <c r="AI26" s="43"/>
-      <c r="AJ26" s="43"/>
-      <c r="AK26" s="43"/>
-      <c r="AL26" s="41"/>
-      <c r="AM26" s="42"/>
-      <c r="AN26" s="42"/>
-      <c r="AO26" s="42"/>
-      <c r="AP26" s="43"/>
-      <c r="AQ26" s="43"/>
-      <c r="AR26" s="43"/>
-      <c r="AS26" s="43"/>
-      <c r="AT26" s="43"/>
-      <c r="AU26" s="43"/>
-      <c r="AV26" s="43"/>
-      <c r="AW26" s="43"/>
-      <c r="AX26" s="43"/>
-      <c r="AY26" s="43"/>
-      <c r="AZ26" s="43"/>
-      <c r="BA26" s="43"/>
+      <c r="A26" s="49"/>
+      <c r="B26" s="49"/>
+      <c r="C26" s="50"/>
+      <c r="D26" s="50"/>
+      <c r="E26" s="50"/>
+      <c r="F26" s="50"/>
+      <c r="G26" s="50"/>
+      <c r="H26" s="50"/>
+      <c r="I26" s="50"/>
+      <c r="J26" s="50"/>
+      <c r="K26" s="50"/>
+      <c r="L26" s="50"/>
+      <c r="M26" s="50"/>
+      <c r="N26" s="50"/>
+      <c r="O26" s="50"/>
+      <c r="P26" s="50"/>
+      <c r="Q26" s="50"/>
+      <c r="R26" s="50"/>
+      <c r="S26" s="50"/>
+      <c r="T26" s="50"/>
+      <c r="U26" s="50"/>
+      <c r="V26" s="50"/>
+      <c r="W26" s="50"/>
+      <c r="X26" s="50"/>
+      <c r="Y26" s="50"/>
+      <c r="Z26" s="50"/>
+      <c r="AA26" s="50"/>
+      <c r="AB26" s="50"/>
+      <c r="AC26" s="50"/>
+      <c r="AD26" s="50"/>
+      <c r="AE26" s="50"/>
+      <c r="AF26" s="50"/>
+      <c r="AG26" s="50"/>
+      <c r="AH26" s="50"/>
+      <c r="AI26" s="50"/>
+      <c r="AJ26" s="50"/>
+      <c r="AK26" s="50"/>
+      <c r="AL26" s="48"/>
+      <c r="AM26" s="49"/>
+      <c r="AN26" s="49"/>
+      <c r="AO26" s="49"/>
+      <c r="AP26" s="50"/>
+      <c r="AQ26" s="50"/>
+      <c r="AR26" s="50"/>
+      <c r="AS26" s="50"/>
+      <c r="AT26" s="50"/>
+      <c r="AU26" s="50"/>
+      <c r="AV26" s="50"/>
+      <c r="AW26" s="50"/>
+      <c r="AX26" s="50"/>
+      <c r="AY26" s="50"/>
+      <c r="AZ26" s="50"/>
+      <c r="BA26" s="50"/>
     </row>
     <row r="27" spans="1:53">
-      <c r="A27" s="42"/>
-      <c r="B27" s="42"/>
-      <c r="C27" s="43"/>
-      <c r="D27" s="43"/>
-      <c r="E27" s="43"/>
-      <c r="F27" s="43"/>
-      <c r="G27" s="43"/>
-      <c r="H27" s="43"/>
-      <c r="I27" s="43"/>
-      <c r="J27" s="43"/>
-      <c r="K27" s="43"/>
-      <c r="L27" s="43"/>
-      <c r="M27" s="43"/>
-      <c r="N27" s="43"/>
-      <c r="O27" s="43"/>
-      <c r="P27" s="43"/>
-      <c r="Q27" s="43"/>
-      <c r="R27" s="43"/>
-      <c r="S27" s="43"/>
-      <c r="T27" s="43"/>
-      <c r="U27" s="43"/>
-      <c r="V27" s="43"/>
-      <c r="W27" s="43"/>
-      <c r="X27" s="43"/>
-      <c r="Y27" s="43"/>
-      <c r="Z27" s="43"/>
-      <c r="AA27" s="43"/>
-      <c r="AB27" s="43"/>
-      <c r="AC27" s="43"/>
-      <c r="AD27" s="43"/>
-      <c r="AE27" s="43"/>
-      <c r="AF27" s="43"/>
-      <c r="AG27" s="43"/>
-      <c r="AH27" s="43"/>
-      <c r="AI27" s="43"/>
-      <c r="AJ27" s="43"/>
-      <c r="AK27" s="43"/>
-      <c r="AL27" s="41"/>
-      <c r="AM27" s="42"/>
-      <c r="AN27" s="42"/>
-      <c r="AO27" s="42"/>
-      <c r="AP27" s="43"/>
-      <c r="AQ27" s="43"/>
-      <c r="AR27" s="43"/>
-      <c r="AS27" s="43"/>
-      <c r="AT27" s="43"/>
-      <c r="AU27" s="43"/>
-      <c r="AV27" s="43"/>
-      <c r="AW27" s="43"/>
-      <c r="AX27" s="43"/>
-      <c r="AY27" s="43"/>
-      <c r="AZ27" s="43"/>
-      <c r="BA27" s="43"/>
+      <c r="A27" s="49"/>
+      <c r="B27" s="49"/>
+      <c r="C27" s="50"/>
+      <c r="D27" s="50"/>
+      <c r="E27" s="50"/>
+      <c r="F27" s="50"/>
+      <c r="G27" s="50"/>
+      <c r="H27" s="50"/>
+      <c r="I27" s="50"/>
+      <c r="J27" s="50"/>
+      <c r="K27" s="50"/>
+      <c r="L27" s="50"/>
+      <c r="M27" s="50"/>
+      <c r="N27" s="50"/>
+      <c r="O27" s="50"/>
+      <c r="P27" s="50"/>
+      <c r="Q27" s="50"/>
+      <c r="R27" s="50"/>
+      <c r="S27" s="50"/>
+      <c r="T27" s="50"/>
+      <c r="U27" s="50"/>
+      <c r="V27" s="50"/>
+      <c r="W27" s="50"/>
+      <c r="X27" s="50"/>
+      <c r="Y27" s="50"/>
+      <c r="Z27" s="50"/>
+      <c r="AA27" s="50"/>
+      <c r="AB27" s="50"/>
+      <c r="AC27" s="50"/>
+      <c r="AD27" s="50"/>
+      <c r="AE27" s="50"/>
+      <c r="AF27" s="50"/>
+      <c r="AG27" s="50"/>
+      <c r="AH27" s="50"/>
+      <c r="AI27" s="50"/>
+      <c r="AJ27" s="50"/>
+      <c r="AK27" s="50"/>
+      <c r="AL27" s="48"/>
+      <c r="AM27" s="49"/>
+      <c r="AN27" s="49"/>
+      <c r="AO27" s="49"/>
+      <c r="AP27" s="50"/>
+      <c r="AQ27" s="50"/>
+      <c r="AR27" s="50"/>
+      <c r="AS27" s="50"/>
+      <c r="AT27" s="50"/>
+      <c r="AU27" s="50"/>
+      <c r="AV27" s="50"/>
+      <c r="AW27" s="50"/>
+      <c r="AX27" s="50"/>
+      <c r="AY27" s="50"/>
+      <c r="AZ27" s="50"/>
+      <c r="BA27" s="50"/>
     </row>
     <row r="28" spans="1:53">
-      <c r="A28" s="42"/>
-      <c r="B28" s="42"/>
-      <c r="C28" s="43"/>
-      <c r="D28" s="43"/>
-      <c r="E28" s="43"/>
-      <c r="F28" s="43"/>
-      <c r="G28" s="43"/>
-      <c r="H28" s="43"/>
-      <c r="I28" s="43"/>
-      <c r="J28" s="43"/>
-      <c r="K28" s="43"/>
-      <c r="L28" s="43"/>
-      <c r="M28" s="43"/>
-      <c r="N28" s="43"/>
-      <c r="O28" s="43"/>
-      <c r="P28" s="43"/>
-      <c r="Q28" s="43"/>
-      <c r="R28" s="43"/>
-      <c r="S28" s="43"/>
-      <c r="T28" s="43"/>
-      <c r="U28" s="43"/>
-      <c r="V28" s="43"/>
-      <c r="W28" s="43"/>
-      <c r="X28" s="43"/>
-      <c r="Y28" s="43"/>
-      <c r="Z28" s="43"/>
-      <c r="AA28" s="43"/>
-      <c r="AB28" s="43"/>
-      <c r="AC28" s="43"/>
-      <c r="AD28" s="43"/>
-      <c r="AE28" s="43"/>
-      <c r="AF28" s="43"/>
-      <c r="AG28" s="43"/>
-      <c r="AH28" s="43"/>
-      <c r="AI28" s="43"/>
-      <c r="AJ28" s="43"/>
-      <c r="AK28" s="43"/>
-      <c r="AL28" s="41"/>
-      <c r="AM28" s="42"/>
-      <c r="AN28" s="42"/>
-      <c r="AO28" s="42"/>
-      <c r="AP28" s="43"/>
-      <c r="AQ28" s="43"/>
-      <c r="AR28" s="43"/>
-      <c r="AS28" s="43"/>
-      <c r="AT28" s="43"/>
-      <c r="AU28" s="43"/>
-      <c r="AV28" s="43"/>
-      <c r="AW28" s="43"/>
-      <c r="AX28" s="43"/>
-      <c r="AY28" s="43"/>
-      <c r="AZ28" s="43"/>
-      <c r="BA28" s="43"/>
+      <c r="A28" s="49"/>
+      <c r="B28" s="49"/>
+      <c r="C28" s="50"/>
+      <c r="D28" s="50"/>
+      <c r="E28" s="50"/>
+      <c r="F28" s="50"/>
+      <c r="G28" s="50"/>
+      <c r="H28" s="50"/>
+      <c r="I28" s="50"/>
+      <c r="J28" s="50"/>
+      <c r="K28" s="50"/>
+      <c r="L28" s="50"/>
+      <c r="M28" s="50"/>
+      <c r="N28" s="50"/>
+      <c r="O28" s="50"/>
+      <c r="P28" s="50"/>
+      <c r="Q28" s="50"/>
+      <c r="R28" s="50"/>
+      <c r="S28" s="50"/>
+      <c r="T28" s="50"/>
+      <c r="U28" s="50"/>
+      <c r="V28" s="50"/>
+      <c r="W28" s="50"/>
+      <c r="X28" s="50"/>
+      <c r="Y28" s="50"/>
+      <c r="Z28" s="50"/>
+      <c r="AA28" s="50"/>
+      <c r="AB28" s="50"/>
+      <c r="AC28" s="50"/>
+      <c r="AD28" s="50"/>
+      <c r="AE28" s="50"/>
+      <c r="AF28" s="50"/>
+      <c r="AG28" s="50"/>
+      <c r="AH28" s="50"/>
+      <c r="AI28" s="50"/>
+      <c r="AJ28" s="50"/>
+      <c r="AK28" s="50"/>
+      <c r="AL28" s="48"/>
+      <c r="AM28" s="49"/>
+      <c r="AN28" s="49"/>
+      <c r="AO28" s="49"/>
+      <c r="AP28" s="50"/>
+      <c r="AQ28" s="50"/>
+      <c r="AR28" s="50"/>
+      <c r="AS28" s="50"/>
+      <c r="AT28" s="50"/>
+      <c r="AU28" s="50"/>
+      <c r="AV28" s="50"/>
+      <c r="AW28" s="50"/>
+      <c r="AX28" s="50"/>
+      <c r="AY28" s="50"/>
+      <c r="AZ28" s="50"/>
+      <c r="BA28" s="50"/>
     </row>
     <row r="29" spans="1:53">
-      <c r="A29" s="42"/>
-      <c r="B29" s="42"/>
-      <c r="C29" s="43"/>
-      <c r="D29" s="43"/>
-      <c r="E29" s="43"/>
-      <c r="F29" s="43"/>
-      <c r="G29" s="43"/>
-      <c r="H29" s="43"/>
-      <c r="I29" s="43"/>
-      <c r="J29" s="43"/>
-      <c r="K29" s="43"/>
-      <c r="L29" s="43"/>
-      <c r="M29" s="43"/>
-      <c r="N29" s="43"/>
-      <c r="O29" s="43"/>
-      <c r="P29" s="43"/>
-      <c r="Q29" s="43"/>
-      <c r="R29" s="43"/>
-      <c r="S29" s="43"/>
-      <c r="T29" s="43"/>
-      <c r="U29" s="43"/>
-      <c r="V29" s="43"/>
-      <c r="W29" s="43"/>
-      <c r="X29" s="43"/>
-      <c r="Y29" s="43"/>
-      <c r="Z29" s="43"/>
-      <c r="AA29" s="43"/>
-      <c r="AB29" s="43"/>
-      <c r="AC29" s="43"/>
-      <c r="AD29" s="43"/>
-      <c r="AE29" s="43"/>
-      <c r="AF29" s="43"/>
-      <c r="AG29" s="43"/>
-      <c r="AH29" s="43"/>
-      <c r="AI29" s="43"/>
-      <c r="AJ29" s="43"/>
-      <c r="AK29" s="43"/>
-      <c r="AL29" s="41"/>
-      <c r="AM29" s="42"/>
-      <c r="AN29" s="42"/>
-      <c r="AO29" s="42"/>
-      <c r="AP29" s="43"/>
-      <c r="AQ29" s="43"/>
-      <c r="AR29" s="43"/>
-      <c r="AS29" s="43"/>
-      <c r="AT29" s="43"/>
-      <c r="AU29" s="43"/>
-      <c r="AV29" s="43"/>
-      <c r="AW29" s="43"/>
-      <c r="AX29" s="43"/>
-      <c r="AY29" s="43"/>
-      <c r="AZ29" s="43"/>
-      <c r="BA29" s="43"/>
+      <c r="A29" s="49"/>
+      <c r="B29" s="49"/>
+      <c r="C29" s="50"/>
+      <c r="D29" s="50"/>
+      <c r="E29" s="50"/>
+      <c r="F29" s="50"/>
+      <c r="G29" s="50"/>
+      <c r="H29" s="50"/>
+      <c r="I29" s="50"/>
+      <c r="J29" s="50"/>
+      <c r="K29" s="50"/>
+      <c r="L29" s="50"/>
+      <c r="M29" s="50"/>
+      <c r="N29" s="50"/>
+      <c r="O29" s="50"/>
+      <c r="P29" s="50"/>
+      <c r="Q29" s="50"/>
+      <c r="R29" s="50"/>
+      <c r="S29" s="50"/>
+      <c r="T29" s="50"/>
+      <c r="U29" s="50"/>
+      <c r="V29" s="50"/>
+      <c r="W29" s="50"/>
+      <c r="X29" s="50"/>
+      <c r="Y29" s="50"/>
+      <c r="Z29" s="50"/>
+      <c r="AA29" s="50"/>
+      <c r="AB29" s="50"/>
+      <c r="AC29" s="50"/>
+      <c r="AD29" s="50"/>
+      <c r="AE29" s="50"/>
+      <c r="AF29" s="50"/>
+      <c r="AG29" s="50"/>
+      <c r="AH29" s="50"/>
+      <c r="AI29" s="50"/>
+      <c r="AJ29" s="50"/>
+      <c r="AK29" s="50"/>
+      <c r="AL29" s="48"/>
+      <c r="AM29" s="49"/>
+      <c r="AN29" s="49"/>
+      <c r="AO29" s="49"/>
+      <c r="AP29" s="50"/>
+      <c r="AQ29" s="50"/>
+      <c r="AR29" s="50"/>
+      <c r="AS29" s="50"/>
+      <c r="AT29" s="50"/>
+      <c r="AU29" s="50"/>
+      <c r="AV29" s="50"/>
+      <c r="AW29" s="50"/>
+      <c r="AX29" s="50"/>
+      <c r="AY29" s="50"/>
+      <c r="AZ29" s="50"/>
+      <c r="BA29" s="50"/>
     </row>
     <row r="30" spans="1:53">
-      <c r="A30" s="42"/>
-      <c r="B30" s="42"/>
-      <c r="C30" s="43"/>
-      <c r="D30" s="43"/>
-      <c r="E30" s="43"/>
-      <c r="F30" s="43"/>
-      <c r="G30" s="43"/>
-      <c r="H30" s="43"/>
-      <c r="I30" s="43"/>
-      <c r="J30" s="43"/>
-      <c r="K30" s="43"/>
-      <c r="L30" s="43"/>
-      <c r="M30" s="43"/>
-      <c r="N30" s="43"/>
-      <c r="O30" s="43"/>
-      <c r="P30" s="43"/>
-      <c r="Q30" s="43"/>
-      <c r="R30" s="43"/>
-      <c r="S30" s="43"/>
-      <c r="T30" s="43"/>
-      <c r="U30" s="43"/>
-      <c r="V30" s="43"/>
-      <c r="W30" s="43"/>
-      <c r="X30" s="43"/>
-      <c r="Y30" s="43"/>
-      <c r="Z30" s="43"/>
-      <c r="AA30" s="43"/>
-      <c r="AB30" s="43"/>
-      <c r="AC30" s="43"/>
-      <c r="AD30" s="43"/>
-      <c r="AE30" s="43"/>
-      <c r="AF30" s="43"/>
-      <c r="AG30" s="43"/>
-      <c r="AH30" s="43"/>
-      <c r="AI30" s="43"/>
-      <c r="AJ30" s="43"/>
-      <c r="AK30" s="43"/>
-      <c r="AL30" s="42"/>
-      <c r="AM30" s="42"/>
-      <c r="AN30" s="42"/>
-      <c r="AO30" s="42"/>
-      <c r="AP30" s="43"/>
-      <c r="AQ30" s="43"/>
-      <c r="AR30" s="43"/>
-      <c r="AS30" s="43"/>
-      <c r="AT30" s="43"/>
-      <c r="AU30" s="43"/>
-      <c r="AV30" s="43"/>
-      <c r="AW30" s="43"/>
-      <c r="AX30" s="43"/>
-      <c r="AY30" s="43"/>
-      <c r="AZ30" s="43"/>
-      <c r="BA30" s="43"/>
+      <c r="A30" s="49"/>
+      <c r="B30" s="49"/>
+      <c r="C30" s="50"/>
+      <c r="D30" s="50"/>
+      <c r="E30" s="50"/>
+      <c r="F30" s="50"/>
+      <c r="G30" s="50"/>
+      <c r="H30" s="50"/>
+      <c r="I30" s="50"/>
+      <c r="J30" s="50"/>
+      <c r="K30" s="50"/>
+      <c r="L30" s="50"/>
+      <c r="M30" s="50"/>
+      <c r="N30" s="50"/>
+      <c r="O30" s="50"/>
+      <c r="P30" s="50"/>
+      <c r="Q30" s="50"/>
+      <c r="R30" s="50"/>
+      <c r="S30" s="50"/>
+      <c r="T30" s="50"/>
+      <c r="U30" s="50"/>
+      <c r="V30" s="50"/>
+      <c r="W30" s="50"/>
+      <c r="X30" s="50"/>
+      <c r="Y30" s="50"/>
+      <c r="Z30" s="50"/>
+      <c r="AA30" s="50"/>
+      <c r="AB30" s="50"/>
+      <c r="AC30" s="50"/>
+      <c r="AD30" s="50"/>
+      <c r="AE30" s="50"/>
+      <c r="AF30" s="50"/>
+      <c r="AG30" s="50"/>
+      <c r="AH30" s="50"/>
+      <c r="AI30" s="50"/>
+      <c r="AJ30" s="50"/>
+      <c r="AK30" s="50"/>
+      <c r="AL30" s="49"/>
+      <c r="AM30" s="49"/>
+      <c r="AN30" s="49"/>
+      <c r="AO30" s="49"/>
+      <c r="AP30" s="50"/>
+      <c r="AQ30" s="50"/>
+      <c r="AR30" s="50"/>
+      <c r="AS30" s="50"/>
+      <c r="AT30" s="50"/>
+      <c r="AU30" s="50"/>
+      <c r="AV30" s="50"/>
+      <c r="AW30" s="50"/>
+      <c r="AX30" s="50"/>
+      <c r="AY30" s="50"/>
+      <c r="AZ30" s="50"/>
+      <c r="BA30" s="50"/>
     </row>
     <row r="31" spans="1:53">
-      <c r="A31" s="42"/>
-      <c r="B31" s="42"/>
-      <c r="C31" s="43"/>
-      <c r="D31" s="43"/>
-      <c r="E31" s="43"/>
-      <c r="F31" s="43"/>
-      <c r="G31" s="43"/>
-      <c r="H31" s="43"/>
-      <c r="I31" s="43"/>
-      <c r="J31" s="43"/>
-      <c r="K31" s="43"/>
-      <c r="L31" s="43"/>
-      <c r="M31" s="43"/>
-      <c r="N31" s="43"/>
-      <c r="O31" s="43"/>
-      <c r="P31" s="43"/>
-      <c r="Q31" s="43"/>
-      <c r="R31" s="43"/>
-      <c r="S31" s="43"/>
-      <c r="T31" s="43"/>
-      <c r="U31" s="43"/>
-      <c r="V31" s="43"/>
-      <c r="W31" s="43"/>
-      <c r="X31" s="43"/>
-      <c r="Y31" s="43"/>
-      <c r="Z31" s="43"/>
-      <c r="AA31" s="43"/>
-      <c r="AB31" s="43"/>
-      <c r="AC31" s="43"/>
-      <c r="AD31" s="43"/>
-      <c r="AE31" s="43"/>
-      <c r="AF31" s="43"/>
-      <c r="AG31" s="43"/>
-      <c r="AH31" s="43"/>
-      <c r="AI31" s="43"/>
-      <c r="AJ31" s="43"/>
-      <c r="AK31" s="43"/>
-      <c r="AL31" s="42"/>
-      <c r="AM31" s="42"/>
-      <c r="AN31" s="42"/>
-      <c r="AO31" s="42"/>
-      <c r="AP31" s="43"/>
-      <c r="AQ31" s="43"/>
-      <c r="AR31" s="43"/>
-      <c r="AS31" s="43"/>
-      <c r="AT31" s="43"/>
-      <c r="AU31" s="43"/>
-      <c r="AV31" s="43"/>
-      <c r="AW31" s="43"/>
-      <c r="AX31" s="43"/>
-      <c r="AY31" s="43"/>
-      <c r="AZ31" s="43"/>
-      <c r="BA31" s="43"/>
+      <c r="A31" s="49"/>
+      <c r="B31" s="49"/>
+      <c r="C31" s="50"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="50"/>
+      <c r="G31" s="50"/>
+      <c r="H31" s="50"/>
+      <c r="I31" s="50"/>
+      <c r="J31" s="50"/>
+      <c r="K31" s="50"/>
+      <c r="L31" s="50"/>
+      <c r="M31" s="50"/>
+      <c r="N31" s="50"/>
+      <c r="O31" s="50"/>
+      <c r="P31" s="50"/>
+      <c r="Q31" s="50"/>
+      <c r="R31" s="50"/>
+      <c r="S31" s="50"/>
+      <c r="T31" s="50"/>
+      <c r="U31" s="50"/>
+      <c r="V31" s="50"/>
+      <c r="W31" s="50"/>
+      <c r="X31" s="50"/>
+      <c r="Y31" s="50"/>
+      <c r="Z31" s="50"/>
+      <c r="AA31" s="50"/>
+      <c r="AB31" s="50"/>
+      <c r="AC31" s="50"/>
+      <c r="AD31" s="50"/>
+      <c r="AE31" s="50"/>
+      <c r="AF31" s="50"/>
+      <c r="AG31" s="50"/>
+      <c r="AH31" s="50"/>
+      <c r="AI31" s="50"/>
+      <c r="AJ31" s="50"/>
+      <c r="AK31" s="50"/>
+      <c r="AL31" s="49"/>
+      <c r="AM31" s="49"/>
+      <c r="AN31" s="49"/>
+      <c r="AO31" s="49"/>
+      <c r="AP31" s="50"/>
+      <c r="AQ31" s="50"/>
+      <c r="AR31" s="50"/>
+      <c r="AS31" s="50"/>
+      <c r="AT31" s="50"/>
+      <c r="AU31" s="50"/>
+      <c r="AV31" s="50"/>
+      <c r="AW31" s="50"/>
+      <c r="AX31" s="50"/>
+      <c r="AY31" s="50"/>
+      <c r="AZ31" s="50"/>
+      <c r="BA31" s="50"/>
     </row>
     <row r="32" spans="1:53">
-      <c r="A32" s="42"/>
-      <c r="B32" s="42"/>
-      <c r="C32" s="43"/>
-      <c r="D32" s="43"/>
-      <c r="E32" s="43"/>
-      <c r="F32" s="43"/>
-      <c r="G32" s="43"/>
-      <c r="H32" s="43"/>
-      <c r="I32" s="43"/>
-      <c r="J32" s="43"/>
-      <c r="K32" s="43"/>
-      <c r="L32" s="43"/>
-      <c r="M32" s="43"/>
-      <c r="N32" s="43"/>
-      <c r="O32" s="43"/>
-      <c r="P32" s="43"/>
-      <c r="Q32" s="43"/>
-      <c r="R32" s="43"/>
-      <c r="S32" s="43"/>
-      <c r="T32" s="43"/>
-      <c r="U32" s="43"/>
-      <c r="V32" s="43"/>
-      <c r="W32" s="43"/>
-      <c r="X32" s="43"/>
-      <c r="Y32" s="43"/>
-      <c r="Z32" s="43"/>
-      <c r="AA32" s="43"/>
-      <c r="AB32" s="43"/>
-      <c r="AC32" s="43"/>
-      <c r="AD32" s="43"/>
-      <c r="AE32" s="43"/>
-      <c r="AF32" s="43"/>
-      <c r="AG32" s="43"/>
-      <c r="AH32" s="43"/>
-      <c r="AI32" s="43"/>
-      <c r="AJ32" s="43"/>
-      <c r="AK32" s="43"/>
-      <c r="AL32" s="42"/>
-      <c r="AM32" s="42"/>
-      <c r="AN32" s="42"/>
-      <c r="AO32" s="42"/>
-      <c r="AP32" s="43"/>
-      <c r="AQ32" s="43"/>
-      <c r="AR32" s="43"/>
-      <c r="AS32" s="43"/>
-      <c r="AT32" s="43"/>
-      <c r="AU32" s="43"/>
-      <c r="AV32" s="43"/>
-      <c r="AW32" s="43"/>
-      <c r="AX32" s="43"/>
-      <c r="AY32" s="43"/>
-      <c r="AZ32" s="43"/>
-      <c r="BA32" s="43"/>
+      <c r="A32" s="49"/>
+      <c r="B32" s="49"/>
+      <c r="C32" s="50"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
+      <c r="F32" s="50"/>
+      <c r="G32" s="50"/>
+      <c r="H32" s="50"/>
+      <c r="I32" s="50"/>
+      <c r="J32" s="50"/>
+      <c r="K32" s="50"/>
+      <c r="L32" s="50"/>
+      <c r="M32" s="50"/>
+      <c r="N32" s="50"/>
+      <c r="O32" s="50"/>
+      <c r="P32" s="50"/>
+      <c r="Q32" s="50"/>
+      <c r="R32" s="50"/>
+      <c r="S32" s="50"/>
+      <c r="T32" s="50"/>
+      <c r="U32" s="50"/>
+      <c r="V32" s="50"/>
+      <c r="W32" s="50"/>
+      <c r="X32" s="50"/>
+      <c r="Y32" s="50"/>
+      <c r="Z32" s="50"/>
+      <c r="AA32" s="50"/>
+      <c r="AB32" s="50"/>
+      <c r="AC32" s="50"/>
+      <c r="AD32" s="50"/>
+      <c r="AE32" s="50"/>
+      <c r="AF32" s="50"/>
+      <c r="AG32" s="50"/>
+      <c r="AH32" s="50"/>
+      <c r="AI32" s="50"/>
+      <c r="AJ32" s="50"/>
+      <c r="AK32" s="50"/>
+      <c r="AL32" s="49"/>
+      <c r="AM32" s="49"/>
+      <c r="AN32" s="49"/>
+      <c r="AO32" s="49"/>
+      <c r="AP32" s="50"/>
+      <c r="AQ32" s="50"/>
+      <c r="AR32" s="50"/>
+      <c r="AS32" s="50"/>
+      <c r="AT32" s="50"/>
+      <c r="AU32" s="50"/>
+      <c r="AV32" s="50"/>
+      <c r="AW32" s="50"/>
+      <c r="AX32" s="50"/>
+      <c r="AY32" s="50"/>
+      <c r="AZ32" s="50"/>
+      <c r="BA32" s="50"/>
     </row>
     <row r="33" spans="1:53">
-      <c r="A33" s="42"/>
-      <c r="B33" s="42"/>
-      <c r="C33" s="43"/>
-      <c r="D33" s="43"/>
-      <c r="E33" s="43"/>
-      <c r="F33" s="43"/>
-      <c r="G33" s="43"/>
-      <c r="H33" s="43"/>
-      <c r="I33" s="43"/>
-      <c r="J33" s="43"/>
-      <c r="K33" s="43"/>
-      <c r="L33" s="43"/>
-      <c r="M33" s="43"/>
-      <c r="N33" s="43"/>
-      <c r="O33" s="43"/>
-      <c r="P33" s="43"/>
-      <c r="Q33" s="43"/>
-      <c r="R33" s="43"/>
-      <c r="S33" s="43"/>
-      <c r="T33" s="43"/>
-      <c r="U33" s="43"/>
-      <c r="V33" s="43"/>
-      <c r="W33" s="43"/>
-      <c r="X33" s="43"/>
-      <c r="Y33" s="43"/>
-      <c r="Z33" s="43"/>
-      <c r="AA33" s="43"/>
-      <c r="AB33" s="43"/>
-      <c r="AC33" s="43"/>
-      <c r="AD33" s="43"/>
-      <c r="AE33" s="43"/>
-      <c r="AF33" s="43"/>
-      <c r="AG33" s="43"/>
-      <c r="AH33" s="43"/>
-      <c r="AI33" s="43"/>
-      <c r="AJ33" s="43"/>
-      <c r="AK33" s="43"/>
-      <c r="AL33" s="42"/>
-      <c r="AM33" s="42"/>
-      <c r="AN33" s="42"/>
-      <c r="AO33" s="42"/>
-      <c r="AP33" s="43"/>
-      <c r="AQ33" s="43"/>
-      <c r="AR33" s="43"/>
-      <c r="AS33" s="43"/>
-      <c r="AT33" s="43"/>
-      <c r="AU33" s="43"/>
-      <c r="AV33" s="43"/>
-      <c r="AW33" s="43"/>
-      <c r="AX33" s="43"/>
-      <c r="AY33" s="43"/>
-      <c r="AZ33" s="43"/>
-      <c r="BA33" s="43"/>
+      <c r="A33" s="49"/>
+      <c r="B33" s="49"/>
+      <c r="C33" s="50"/>
+      <c r="D33" s="50"/>
+      <c r="E33" s="50"/>
+      <c r="F33" s="50"/>
+      <c r="G33" s="50"/>
+      <c r="H33" s="50"/>
+      <c r="I33" s="50"/>
+      <c r="J33" s="50"/>
+      <c r="K33" s="50"/>
+      <c r="L33" s="50"/>
+      <c r="M33" s="50"/>
+      <c r="N33" s="50"/>
+      <c r="O33" s="50"/>
+      <c r="P33" s="50"/>
+      <c r="Q33" s="50"/>
+      <c r="R33" s="50"/>
+      <c r="S33" s="50"/>
+      <c r="T33" s="50"/>
+      <c r="U33" s="50"/>
+      <c r="V33" s="50"/>
+      <c r="W33" s="50"/>
+      <c r="X33" s="50"/>
+      <c r="Y33" s="50"/>
+      <c r="Z33" s="50"/>
+      <c r="AA33" s="50"/>
+      <c r="AB33" s="50"/>
+      <c r="AC33" s="50"/>
+      <c r="AD33" s="50"/>
+      <c r="AE33" s="50"/>
+      <c r="AF33" s="50"/>
+      <c r="AG33" s="50"/>
+      <c r="AH33" s="50"/>
+      <c r="AI33" s="50"/>
+      <c r="AJ33" s="50"/>
+      <c r="AK33" s="50"/>
+      <c r="AL33" s="49"/>
+      <c r="AM33" s="49"/>
+      <c r="AN33" s="49"/>
+      <c r="AO33" s="49"/>
+      <c r="AP33" s="50"/>
+      <c r="AQ33" s="50"/>
+      <c r="AR33" s="50"/>
+      <c r="AS33" s="50"/>
+      <c r="AT33" s="50"/>
+      <c r="AU33" s="50"/>
+      <c r="AV33" s="50"/>
+      <c r="AW33" s="50"/>
+      <c r="AX33" s="50"/>
+      <c r="AY33" s="50"/>
+      <c r="AZ33" s="50"/>
+      <c r="BA33" s="50"/>
     </row>
     <row r="34" spans="1:53">
-      <c r="A34" s="42"/>
-      <c r="B34" s="42"/>
-      <c r="C34" s="43"/>
-      <c r="D34" s="43"/>
-      <c r="E34" s="43"/>
-      <c r="F34" s="43"/>
-      <c r="G34" s="43"/>
-      <c r="H34" s="43"/>
-      <c r="I34" s="43"/>
-      <c r="J34" s="43"/>
-      <c r="K34" s="43"/>
-      <c r="L34" s="43"/>
-      <c r="M34" s="43"/>
-      <c r="N34" s="43"/>
-      <c r="O34" s="43"/>
-      <c r="P34" s="43"/>
-      <c r="Q34" s="43"/>
-      <c r="R34" s="43"/>
-      <c r="S34" s="43"/>
-      <c r="T34" s="43"/>
-      <c r="U34" s="43"/>
-      <c r="V34" s="43"/>
-      <c r="W34" s="43"/>
-      <c r="X34" s="43"/>
-      <c r="Y34" s="43"/>
-      <c r="Z34" s="43"/>
-      <c r="AA34" s="43"/>
-      <c r="AB34" s="43"/>
-      <c r="AC34" s="43"/>
-      <c r="AD34" s="43"/>
-      <c r="AE34" s="43"/>
-      <c r="AF34" s="43"/>
-      <c r="AG34" s="43"/>
-      <c r="AH34" s="43"/>
-      <c r="AI34" s="43"/>
-      <c r="AJ34" s="43"/>
-      <c r="AK34" s="43"/>
-      <c r="AL34" s="42"/>
-      <c r="AM34" s="42"/>
-      <c r="AN34" s="42"/>
-      <c r="AO34" s="42"/>
-      <c r="AP34" s="43"/>
-      <c r="AQ34" s="43"/>
-      <c r="AR34" s="43"/>
-      <c r="AS34" s="43"/>
-      <c r="AT34" s="43"/>
-      <c r="AU34" s="43"/>
-      <c r="AV34" s="43"/>
-      <c r="AW34" s="43"/>
-      <c r="AX34" s="43"/>
-      <c r="AY34" s="43"/>
-      <c r="AZ34" s="43"/>
-      <c r="BA34" s="43"/>
+      <c r="A34" s="49"/>
+      <c r="B34" s="49"/>
+      <c r="C34" s="50"/>
+      <c r="D34" s="50"/>
+      <c r="E34" s="50"/>
+      <c r="F34" s="50"/>
+      <c r="G34" s="50"/>
+      <c r="H34" s="50"/>
+      <c r="I34" s="50"/>
+      <c r="J34" s="50"/>
+      <c r="K34" s="50"/>
+      <c r="L34" s="50"/>
+      <c r="M34" s="50"/>
+      <c r="N34" s="50"/>
+      <c r="O34" s="50"/>
+      <c r="P34" s="50"/>
+      <c r="Q34" s="50"/>
+      <c r="R34" s="50"/>
+      <c r="S34" s="50"/>
+      <c r="T34" s="50"/>
+      <c r="U34" s="50"/>
+      <c r="V34" s="50"/>
+      <c r="W34" s="50"/>
+      <c r="X34" s="50"/>
+      <c r="Y34" s="50"/>
+      <c r="Z34" s="50"/>
+      <c r="AA34" s="50"/>
+      <c r="AB34" s="50"/>
+      <c r="AC34" s="50"/>
+      <c r="AD34" s="50"/>
+      <c r="AE34" s="50"/>
+      <c r="AF34" s="50"/>
+      <c r="AG34" s="50"/>
+      <c r="AH34" s="50"/>
+      <c r="AI34" s="50"/>
+      <c r="AJ34" s="50"/>
+      <c r="AK34" s="50"/>
+      <c r="AL34" s="49"/>
+      <c r="AM34" s="49"/>
+      <c r="AN34" s="49"/>
+      <c r="AO34" s="49"/>
+      <c r="AP34" s="50"/>
+      <c r="AQ34" s="50"/>
+      <c r="AR34" s="50"/>
+      <c r="AS34" s="50"/>
+      <c r="AT34" s="50"/>
+      <c r="AU34" s="50"/>
+      <c r="AV34" s="50"/>
+      <c r="AW34" s="50"/>
+      <c r="AX34" s="50"/>
+      <c r="AY34" s="50"/>
+      <c r="AZ34" s="50"/>
+      <c r="BA34" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="229">
@@ -7055,33 +7077,33 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CE690AC-D5C7-474D-85FA-6AAB1896A401}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="29.375" customWidth="1"/>
-    <col min="2" max="2" width="30.125" customWidth="1"/>
-    <col min="3" max="3" width="39.875" customWidth="1"/>
+    <col min="2" max="2" width="47.75" customWidth="1"/>
+    <col min="3" max="3" width="47.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="14.25" thickBot="1">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="23" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="14.25" thickTop="1">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="22" t="s">
         <v>52</v>
       </c>
     </row>
@@ -7089,7 +7111,7 @@
       <c r="A3" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="32" t="s">
         <v>61</v>
       </c>
       <c r="C3" s="21" t="s">
@@ -7111,7 +7133,7 @@
       <c r="A5" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="37" t="s">
         <v>39</v>
       </c>
       <c r="C5" s="21" t="s">
@@ -7141,86 +7163,123 @@
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="26"/>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="30" t="s">
+      <c r="A9" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="C9" s="31" t="s">
+      <c r="C9" s="30" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="26" t="s">
+      <c r="A10" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
+      <c r="B10" s="26"/>
+      <c r="C10" s="26"/>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="28" t="s">
+      <c r="A11" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29" t="s">
+      <c r="B11" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" s="28" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="28" t="s">
+      <c r="A12" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="B12" s="29"/>
-      <c r="C12" s="29" t="s">
+      <c r="B12" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="C12" s="28" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="30" t="s">
+      <c r="A13" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="B13" s="31"/>
-      <c r="C13" s="31" t="s">
+      <c r="B13" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" s="30" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="88" t="s">
+      <c r="A14" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="B14" s="34" t="s">
+      <c r="B14" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="89" t="s">
+      <c r="C14" s="35" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="90" t="s">
+      <c r="A15" s="34" t="s">
         <v>68</v>
       </c>
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="35" t="s">
         <v>69</v>
       </c>
-      <c r="C15" s="22" t="s">
+      <c r="C15" s="37" t="s">
         <v>70</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="C16" s="35" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="38" t="s">
+        <v>74</v>
+      </c>
+      <c r="B17" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="C17" s="35" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="39"/>
+      <c r="B18" s="36"/>
+      <c r="C18" s="40" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" s="22"/>
+      <c r="B19" s="36"/>
+      <c r="C19" s="41" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="52"/>
-  <hyperlinks>
-    <hyperlink ref="B5" r:id="rId1" xr:uid="{393A6AE7-BE99-4ADD-9D05-CEFF33ED5496}"/>
-    <hyperlink ref="B15" r:id="rId2" xr:uid="{E27396FF-ACBC-4E31-9BDB-8719F504B017}"/>
-    <hyperlink ref="C15" r:id="rId3" xr:uid="{99BDA459-FD76-4B92-A579-D5A3A29EC344}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -7231,12 +7290,12 @@
   <sheetFormatPr defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:1">
-      <c r="A2" s="32"/>
+      <c r="A2" s="31"/>
     </row>
   </sheetData>
   <phoneticPr fontId="52"/>
